--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1471,7 +1471,9 @@
         <v>3</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1517,7 +1519,9 @@
         <v>4</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1563,7 +1567,9 @@
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1609,7 +1615,9 @@
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1654,7 +1662,11 @@
       <c r="I6" t="n">
         <v>6</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
@@ -1700,7 +1712,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
@@ -1746,7 +1762,11 @@
       <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
@@ -3921,7 +3941,9 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>100</v>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3965,7 +3987,9 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>100</v>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4011,7 +4035,9 @@
         <v>4</v>
       </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>100</v>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4057,7 +4083,9 @@
         <v>4</v>
       </c>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>100</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4103,7 +4131,9 @@
         <v>4</v>
       </c>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>100</v>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4149,7 +4179,9 @@
         <v>4</v>
       </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>100</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -7123,7 +7155,9 @@
         <v>3</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -7169,7 +7203,9 @@
         <v>4</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -7215,7 +7251,9 @@
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -7261,7 +7299,9 @@
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -7360,7 +7400,11 @@
       <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
@@ -7406,7 +7450,11 @@
       <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
@@ -7452,7 +7500,11 @@
       <c r="I9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
@@ -9535,7 +9587,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -9589,7 +9641,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -10239,7 +10291,9 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>100</v>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10283,7 +10337,9 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>100</v>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10329,7 +10385,9 @@
         <v>4</v>
       </c>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>100</v>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10375,7 +10433,9 @@
         <v>4</v>
       </c>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>100</v>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10421,7 +10481,9 @@
         <v>4</v>
       </c>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>100</v>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10467,7 +10529,9 @@
         <v>4</v>
       </c>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>100</v>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -2942,8 +2942,14 @@
         <v>0.02</v>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PTBLWTHM0004</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1000</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -2986,7 +2992,11 @@
         <v>1.81</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PTIXAEHM0006</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
@@ -3854,8 +3864,14 @@
       <c r="I54" t="n">
         <v>4</v>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PTYESALM0007</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>25</v>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3896,8 +3912,14 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4272,7 +4294,11 @@
       <c r="I63" t="n">
         <v>5</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PTOPZEHM0017</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
@@ -4318,7 +4344,11 @@
       <c r="I64" t="n">
         <v>4</v>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PTOPZAHM0003</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
@@ -4364,7 +4394,11 @@
       <c r="I65" t="n">
         <v>4</v>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PTOPZBHM0002</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
@@ -4410,7 +4444,11 @@
       <c r="I66" t="n">
         <v>4</v>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PTOPZDHM0000</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
@@ -6618,7 +6656,11 @@
       <c r="I115" t="n">
         <v>3</v>
       </c>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
@@ -6664,7 +6706,11 @@
       <c r="I116" t="n">
         <v>3</v>
       </c>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
@@ -6710,7 +6756,11 @@
       <c r="I117" t="n">
         <v>3</v>
       </c>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
@@ -6756,7 +6806,11 @@
       <c r="I118" t="n">
         <v>3</v>
       </c>
-      <c r="J118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
@@ -6802,7 +6856,11 @@
       <c r="I119" t="n">
         <v>4</v>
       </c>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
@@ -6848,7 +6906,11 @@
       <c r="I120" t="n">
         <v>4</v>
       </c>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
@@ -6894,7 +6956,11 @@
       <c r="I121" t="n">
         <v>4</v>
       </c>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
@@ -8680,8 +8746,14 @@
         <v>0.02</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PTBLWTHM0004</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1000</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -8724,7 +8796,11 @@
         <v>1.81</v>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PTIXAEHM0006</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
@@ -9700,8 +9776,14 @@
       <c r="I57" t="n">
         <v>4</v>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PTYESALM0007</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>25</v>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9742,8 +9824,14 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>5</v>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10622,7 +10710,11 @@
       <c r="I78" t="n">
         <v>5</v>
       </c>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PTOPZEHM0017</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
@@ -10668,7 +10760,11 @@
       <c r="I79" t="n">
         <v>4</v>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PTOPZAHM0003</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
@@ -10714,7 +10810,11 @@
       <c r="I80" t="n">
         <v>4</v>
       </c>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PTOPZBHM0002</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
@@ -10760,7 +10860,11 @@
       <c r="I81" t="n">
         <v>4</v>
       </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PTOPZDHM0000</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
@@ -13178,7 +13282,11 @@
       <c r="I135" t="n">
         <v>3</v>
       </c>
-      <c r="J135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
@@ -13224,7 +13332,11 @@
       <c r="I136" t="n">
         <v>3</v>
       </c>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
@@ -13270,7 +13382,11 @@
       <c r="I137" t="n">
         <v>3</v>
       </c>
-      <c r="J137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
@@ -13316,7 +13432,11 @@
       <c r="I138" t="n">
         <v>3</v>
       </c>
-      <c r="J138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
@@ -13362,7 +13482,11 @@
       <c r="I139" t="n">
         <v>4</v>
       </c>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
@@ -13408,7 +13532,11 @@
       <c r="I140" t="n">
         <v>4</v>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
@@ -13454,7 +13582,11 @@
       <c r="I141" t="n">
         <v>4</v>
       </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -678,10 +678,18 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PTFP00000762</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10000</v>
+      </c>
       <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -720,10 +728,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PTFP00000861</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1500</v>
+      </c>
       <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -764,7 +780,11 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PTFP00000416</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -806,7 +826,11 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PTFP00000424</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -848,7 +872,11 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PTFP00000382</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -890,7 +918,11 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PTFP00000432</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -974,7 +1006,11 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PTFP00000515</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -1016,7 +1052,11 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PTFP00000879</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -1058,7 +1098,11 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PTFP00000507</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -1100,7 +1144,11 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PTFP00000473</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -1184,7 +1232,11 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1268,7 +1320,11 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -2034,7 +2090,11 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
@@ -2076,7 +2136,11 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
@@ -2118,7 +2182,11 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
@@ -2164,7 +2232,11 @@
       <c r="I17" t="n">
         <v>4</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
@@ -2210,7 +2282,11 @@
       <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -2256,7 +2332,11 @@
       <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
@@ -2302,7 +2382,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PTYBCFHM0017</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
@@ -2348,7 +2432,11 @@
       <c r="I21" t="n">
         <v>4</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PTYBCFHM0017</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
@@ -2394,7 +2482,11 @@
       <c r="I22" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PTYBCFHM0017</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
@@ -2440,7 +2532,11 @@
       <c r="I23" t="n">
         <v>5</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
@@ -2486,7 +2582,11 @@
       <c r="I24" t="n">
         <v>5</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
@@ -2532,7 +2632,11 @@
       <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
@@ -3042,7 +3146,11 @@
       <c r="I36" t="n">
         <v>5</v>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
@@ -3088,7 +3196,11 @@
       <c r="I37" t="n">
         <v>5</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
@@ -3134,7 +3246,11 @@
       <c r="I38" t="n">
         <v>5</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
@@ -3180,7 +3296,11 @@
       <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
@@ -3224,7 +3344,11 @@
         <v>1.83</v>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
@@ -3268,7 +3392,11 @@
         <v>1.68</v>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
@@ -3312,7 +3440,11 @@
         <v>1.47</v>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
@@ -3358,7 +3490,11 @@
       <c r="I43" t="n">
         <v>4</v>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
@@ -3404,7 +3540,11 @@
       <c r="I44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
@@ -3450,7 +3590,11 @@
       <c r="I45" t="n">
         <v>4</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
@@ -3496,7 +3640,11 @@
       <c r="I46" t="n">
         <v>4</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
@@ -3542,7 +3690,11 @@
       <c r="I47" t="n">
         <v>4</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
@@ -3588,7 +3740,11 @@
       <c r="I48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
@@ -3634,7 +3790,11 @@
       <c r="I49" t="n">
         <v>4</v>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
@@ -3680,7 +3840,11 @@
       <c r="I50" t="n">
         <v>4</v>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
@@ -6518,8 +6682,14 @@
       <c r="I112" t="n">
         <v>5</v>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>10000</v>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -6564,8 +6734,14 @@
       <c r="I113" t="n">
         <v>5</v>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>500000</v>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -6610,8 +6786,14 @@
       <c r="I114" t="n">
         <v>5</v>
       </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1000</v>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -7006,7 +7188,11 @@
       <c r="I122" t="n">
         <v>3</v>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PTSFFAHM0013</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
@@ -7052,7 +7238,11 @@
       <c r="I123" t="n">
         <v>3</v>
       </c>
-      <c r="J123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
@@ -7098,7 +7288,11 @@
       <c r="I124" t="n">
         <v>3</v>
       </c>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
@@ -7838,7 +8032,11 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
@@ -7880,7 +8078,11 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
@@ -7922,7 +8124,11 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
@@ -7968,7 +8174,11 @@
       <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -8014,7 +8224,11 @@
       <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
@@ -8060,7 +8274,11 @@
       <c r="I20" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
@@ -8106,7 +8324,11 @@
       <c r="I21" t="n">
         <v>4</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PTYBCFHM0017</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
@@ -8152,7 +8374,11 @@
       <c r="I22" t="n">
         <v>4</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PTYBCFHM0017</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
@@ -8198,7 +8424,11 @@
       <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PTYBCFHM0017</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
@@ -8244,7 +8474,11 @@
       <c r="I24" t="n">
         <v>5</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
@@ -8290,7 +8524,11 @@
       <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
@@ -8336,7 +8574,11 @@
       <c r="I26" t="n">
         <v>5</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
@@ -8846,7 +9088,11 @@
       <c r="I37" t="n">
         <v>5</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
@@ -8892,7 +9138,11 @@
       <c r="I38" t="n">
         <v>5</v>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
@@ -8938,7 +9188,11 @@
       <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
@@ -8984,7 +9238,11 @@
       <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
@@ -9028,7 +9286,11 @@
         <v>1.83</v>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
@@ -9072,7 +9334,11 @@
         <v>1.68</v>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
@@ -9116,7 +9382,11 @@
         <v>1.47</v>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
@@ -9162,7 +9432,11 @@
       <c r="I44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
@@ -9208,7 +9482,11 @@
       <c r="I45" t="n">
         <v>4</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
@@ -9254,7 +9532,11 @@
       <c r="I46" t="n">
         <v>4</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
@@ -9300,7 +9582,11 @@
       <c r="I47" t="n">
         <v>4</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
@@ -9346,7 +9632,11 @@
       <c r="I48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
@@ -9392,7 +9682,11 @@
       <c r="I49" t="n">
         <v>4</v>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
@@ -9438,7 +9732,11 @@
       <c r="I50" t="n">
         <v>4</v>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
@@ -9484,7 +9782,11 @@
       <c r="I51" t="n">
         <v>4</v>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
@@ -9874,10 +10176,18 @@
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PTFP00000762</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>10000</v>
+      </c>
       <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -9916,10 +10226,18 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PTFP00000861</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1500</v>
+      </c>
       <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -9960,7 +10278,11 @@
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PTFP00000416</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
     </row>
@@ -10002,7 +10324,11 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PTFP00000424</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -10044,7 +10370,11 @@
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PTFP00000382</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -10086,7 +10416,11 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PTFP00000432</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -10170,7 +10504,11 @@
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PTFP00000515</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
     </row>
@@ -10212,7 +10550,11 @@
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PTFP00000879</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
     </row>
@@ -10254,7 +10596,11 @@
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PTFP00000507</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
     </row>
@@ -10296,7 +10642,11 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PTFP00000473</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
     </row>
@@ -12934,8 +13284,14 @@
       <c r="I127" t="n">
         <v>5</v>
       </c>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>10000</v>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -12980,8 +13336,14 @@
       <c r="I128" t="n">
         <v>5</v>
       </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>500000</v>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -13026,8 +13388,14 @@
       <c r="I129" t="n">
         <v>5</v>
       </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>1000</v>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -13072,7 +13440,11 @@
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
     </row>
@@ -13156,7 +13528,11 @@
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
     </row>
@@ -13632,7 +14008,11 @@
       <c r="I142" t="n">
         <v>3</v>
       </c>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PTSFFAHM0013</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
@@ -13678,7 +14058,11 @@
       <c r="I143" t="n">
         <v>3</v>
       </c>
-      <c r="J143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
@@ -13724,7 +14108,11 @@
       <c r="I144" t="n">
         <v>3</v>
       </c>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -4653,12 +4653,16 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I67" t="n">
         <v>4</v>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
@@ -4699,13 +4703,19 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I68" t="n">
         <v>4</v>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>100000</v>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4745,13 +4755,19 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I69" t="n">
         <v>4</v>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>100000</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4791,13 +4807,19 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I70" t="n">
         <v>4</v>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>100000</v>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4837,13 +4859,19 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I71" t="n">
         <v>4</v>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>100000</v>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4883,13 +4911,19 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I72" t="n">
         <v>4</v>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PTOYADHM0008</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>100000</v>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4929,13 +4963,19 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I73" t="n">
         <v>4</v>
       </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PTOYAEHM0007</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>100000</v>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4974,12 +5014,20 @@
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I74" t="n">
         <v>4</v>
       </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PTOYAFHM0006</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>100000</v>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5019,12 +5067,16 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I75" t="n">
         <v>4</v>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PTOXCTHM0009</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
@@ -5065,13 +5117,19 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>100000</v>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5110,12 +5168,20 @@
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I77" t="n">
         <v>4</v>
       </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PTOYAIHM0003</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>100000</v>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5154,12 +5220,20 @@
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I78" t="n">
         <v>4</v>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PTOYAJHM0002</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>100000</v>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5198,12 +5272,20 @@
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I79" t="n">
         <v>4</v>
       </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PTOYAKHM0009</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>100000</v>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5242,12 +5324,20 @@
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I80" t="n">
         <v>4</v>
       </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PTOYALHM0008</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>100000</v>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5286,12 +5376,20 @@
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I81" t="n">
         <v>4</v>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PTOYAMHM0007</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>100000</v>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5331,12 +5429,16 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I82" t="n">
         <v>4</v>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
@@ -5377,12 +5479,16 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I83" t="n">
         <v>4</v>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
@@ -5423,12 +5529,16 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>4</v>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PTOYARHM0002</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
@@ -5469,12 +5579,16 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I85" t="n">
         <v>4</v>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
@@ -5515,12 +5629,16 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I86" t="n">
         <v>4</v>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PTOYATHM0000</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
@@ -5560,11 +5678,17 @@
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I87" t="n">
         <v>4</v>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PTOYAUHM0007</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
@@ -5604,11 +5728,17 @@
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I88" t="n">
         <v>4</v>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PTOYAVHM0006</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
@@ -5648,11 +5778,17 @@
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I89" t="n">
         <v>4</v>
       </c>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PTOYAWHM0005</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
@@ -5692,11 +5828,17 @@
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I90" t="n">
         <v>4</v>
       </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PTOYAXHM0004</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
@@ -5736,11 +5878,17 @@
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I91" t="n">
         <v>4</v>
       </c>
-      <c r="J91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PTOXS3HM0000</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
@@ -5780,11 +5928,17 @@
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I92" t="n">
         <v>4</v>
       </c>
-      <c r="J92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PTOXS4HM0009</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
@@ -5824,11 +5978,17 @@
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I93" t="n">
         <v>4</v>
       </c>
-      <c r="J93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PTOXS5HM0008</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
@@ -5913,13 +6073,19 @@
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>2000</v>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5959,13 +6125,19 @@
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>2000</v>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6005,13 +6177,19 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
       </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>2000</v>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6051,13 +6229,19 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I98" t="n">
         <v>4</v>
       </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>2000</v>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6097,13 +6281,19 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I99" t="n">
         <v>4</v>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PTOYA2HM0007</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>2000</v>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6143,13 +6333,19 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I100" t="n">
         <v>4</v>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>PTOYA3HM0006</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>2000</v>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6189,13 +6385,19 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I101" t="n">
         <v>4</v>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PTOYA4HM0005</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>2000</v>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6235,13 +6437,19 @@
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I102" t="n">
         <v>4</v>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>PTOYA5HM0004</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>2000</v>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6280,12 +6488,20 @@
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I103" t="n">
         <v>4</v>
       </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>PTOYA6HM0003</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>2000</v>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6324,12 +6540,20 @@
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I104" t="n">
         <v>4</v>
       </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>PTOXSMHM0008</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>2000</v>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6368,12 +6592,20 @@
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I105" t="n">
         <v>4</v>
       </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PTOXSNHM0007</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>2000</v>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6412,12 +6644,20 @@
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I106" t="n">
         <v>4</v>
       </c>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>PTOXSOHM0006</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>2000</v>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6456,12 +6696,20 @@
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I107" t="n">
         <v>4</v>
       </c>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>PTOXSPHM0005</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>2000</v>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6500,12 +6748,20 @@
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I108" t="n">
         <v>4</v>
       </c>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>PTOXS6HM0007</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>2000</v>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6544,12 +6800,20 @@
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I109" t="n">
         <v>4</v>
       </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>PTOXS7HM0006</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>2000</v>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6588,12 +6852,20 @@
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I110" t="n">
         <v>4</v>
       </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>PTOXS8HM0005</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>2000</v>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6632,12 +6904,20 @@
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I111" t="n">
         <v>4</v>
       </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>PTOXS9HM0004</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>2000</v>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11255,12 +11535,16 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I82" t="n">
         <v>4</v>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
@@ -11301,13 +11585,19 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I83" t="n">
         <v>4</v>
       </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>100000</v>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11347,13 +11637,19 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I84" t="n">
         <v>4</v>
       </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>100000</v>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11393,13 +11689,19 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I85" t="n">
         <v>4</v>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>100000</v>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11439,13 +11741,19 @@
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I86" t="n">
         <v>4</v>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>100000</v>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11485,13 +11793,19 @@
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I87" t="n">
         <v>4</v>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PTOYADHM0008</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>100000</v>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11531,13 +11845,19 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I88" t="n">
         <v>4</v>
       </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PTOYAEHM0007</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>100000</v>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11576,12 +11896,20 @@
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I89" t="n">
         <v>4</v>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PTOYAFHM0006</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>100000</v>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11621,12 +11949,16 @@
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="I90" t="n">
         <v>4</v>
       </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PTOXCTHM0009</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
@@ -11667,13 +11999,19 @@
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="I91" t="n">
         <v>4</v>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>100000</v>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11712,12 +12050,20 @@
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I92" t="n">
         <v>4</v>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PTOYAIHM0003</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>100000</v>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11756,12 +12102,20 @@
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I93" t="n">
         <v>4</v>
       </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PTOYAJHM0002</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>100000</v>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11800,12 +12154,20 @@
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I94" t="n">
         <v>4</v>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>PTOYAKHM0009</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>100000</v>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11844,12 +12206,20 @@
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I95" t="n">
         <v>4</v>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>PTOYALHM0008</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>100000</v>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11888,12 +12258,20 @@
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>0.76</v>
+      </c>
       <c r="I96" t="n">
         <v>4</v>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PTOYAMHM0007</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>100000</v>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -11933,12 +12311,16 @@
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
       </c>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
@@ -11979,12 +12361,16 @@
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I98" t="n">
         <v>4</v>
       </c>
-      <c r="J98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
@@ -12025,12 +12411,16 @@
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I99" t="n">
         <v>4</v>
       </c>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PTOYARHM0002</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
@@ -12071,12 +12461,16 @@
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I100" t="n">
         <v>4</v>
       </c>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
@@ -12117,12 +12511,16 @@
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
         <v>4</v>
       </c>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PTOYATHM0000</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
@@ -12162,11 +12560,17 @@
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I102" t="n">
         <v>4</v>
       </c>
-      <c r="J102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>PTOYAUHM0007</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
@@ -12206,11 +12610,17 @@
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I103" t="n">
         <v>4</v>
       </c>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>PTOYAVHM0006</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
@@ -12250,11 +12660,17 @@
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I104" t="n">
         <v>4</v>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>PTOYAWHM0005</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
@@ -12294,11 +12710,17 @@
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I105" t="n">
         <v>4</v>
       </c>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PTOYAXHM0004</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
@@ -12338,11 +12760,17 @@
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I106" t="n">
         <v>4</v>
       </c>
-      <c r="J106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>PTOXS3HM0000</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
@@ -12382,11 +12810,17 @@
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I107" t="n">
         <v>4</v>
       </c>
-      <c r="J107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>PTOXS4HM0009</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
@@ -12426,11 +12860,17 @@
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I108" t="n">
         <v>4</v>
       </c>
-      <c r="J108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>PTOXS5HM0008</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
@@ -12515,13 +12955,19 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I110" t="n">
         <v>4</v>
       </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>2000</v>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12561,13 +13007,19 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I111" t="n">
         <v>4</v>
       </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>2000</v>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12607,13 +13059,19 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I112" t="n">
         <v>4</v>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>2000</v>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12653,13 +13111,19 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I113" t="n">
         <v>4</v>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>2000</v>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12699,13 +13163,19 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I114" t="n">
         <v>4</v>
       </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>PTOYA2HM0007</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>2000</v>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12745,13 +13215,19 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I115" t="n">
         <v>4</v>
       </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>PTOYA3HM0006</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>2000</v>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12791,13 +13267,19 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I116" t="n">
         <v>4</v>
       </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>PTOYA4HM0005</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>2000</v>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12837,13 +13319,19 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I117" t="n">
         <v>4</v>
       </c>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>PTOYA5HM0004</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>2000</v>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12882,12 +13370,20 @@
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I118" t="n">
         <v>4</v>
       </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>PTOYA6HM0003</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>2000</v>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12926,12 +13422,20 @@
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I119" t="n">
         <v>4</v>
       </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>PTOXSMHM0008</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>2000</v>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -12970,12 +13474,20 @@
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I120" t="n">
         <v>4</v>
       </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>PTOXSNHM0007</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>2000</v>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -13014,12 +13526,20 @@
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I121" t="n">
         <v>4</v>
       </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PTOXSOHM0006</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>2000</v>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -13058,12 +13578,20 @@
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I122" t="n">
         <v>4</v>
       </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PTOXSPHM0005</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>2000</v>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -13102,12 +13630,20 @@
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I123" t="n">
         <v>4</v>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PTOXS6HM0007</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>2000</v>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -13146,12 +13682,20 @@
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I124" t="n">
         <v>4</v>
       </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>PTOXS7HM0006</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>2000</v>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -13190,12 +13734,20 @@
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I125" t="n">
         <v>4</v>
       </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>PTOXS8HM0005</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>2000</v>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -13234,12 +13786,20 @@
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I126" t="n">
         <v>4</v>
       </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>PTOXS9HM0004</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>2000</v>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,22 +537,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>casa-inv-sg-founders</t>
+          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-306</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Founders</t>
+          <t>BANKINTER MEGA TT PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>BANKINTER MEGA TT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,18 +567,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.45</v>
+        <v>2.51</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PTCUUBHM0004</t>
+          <t>PTBKCAHM0000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -591,22 +591,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>casa-inv-sg-prime</t>
+          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-307</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Prime</t>
+          <t>BANKINTER MEGA TT PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>BANKINTER MEGA TT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -621,18 +621,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PTCUUAHM0005</t>
+          <t>PTBKCAHM0000</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -645,22 +645,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-plus</t>
+          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-308</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Plus</t>
+          <t>BANKINTER MEGA TT PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>BANKINTER MEGA TT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -670,47 +670,51 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>1.99</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PTFP00000762</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-start</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Start</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -720,47 +724,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PTFP00000861</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-ativa</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Ativa</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -770,7 +774,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -782,31 +786,35 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PTFP00000416</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-conservadora</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Conservadora</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -828,31 +836,35 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PTFP00000424</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-dinamica</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Dinâmica</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -862,7 +874,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -870,35 +882,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PTFP00000382</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-equilibrada</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Equilibrada</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -908,7 +928,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -916,35 +936,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PTFP00000432</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-garantida</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Garantida</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -954,7 +982,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -962,31 +990,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PTYBCPLM0001</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-conservadora</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Conservadora</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,7 +1036,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1004,35 +1044,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PTFP00000515</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-dinamica</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Dinâmica</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1042,7 +1090,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1050,35 +1098,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PTFP00000879</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-equilibrada</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Equilibrada</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1088,7 +1144,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1096,35 +1152,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PTFP00000507</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-garantida</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Garantida</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1134,7 +1198,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1142,35 +1206,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PTFP00000473</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>golden-sgf-top-gestores</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Golden SGF TOP GESTORES</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1180,7 +1252,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1188,31 +1260,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PTYBCQLM0000</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1222,7 +1306,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1230,35 +1314,43 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1268,39 +1360,51 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1310,43 +1414,51 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTFP00000770</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1356,61 +1468,2157 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH ARROJADO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH AÇÕES</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH AÇÕES</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH AÇÕES</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CAIXA WEALTH MODERADO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>casa-inv-sg-founders</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Casa de Investimentos Save &amp; Grow PPR — Founders</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Casa de Investimentos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>investing</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PTCUUBHM0004</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>casa-inv-sg-prime</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Casa de Investimentos Save &amp; Grow PPR — Prime</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Casa de Investimentos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>investing</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PTCUUAHM0005</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GNB PPR/OICVM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GNB PPR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PTYESALM0007</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>golden-sgf-etf-plus</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Golden SGF ETF Plus</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PTFP00000762</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>golden-sgf-etf-start</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Golden SGF ETF Start</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PTFP00000861</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>golden-sgf-poupanca-ativa</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Golden SGF Poupança Ativa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PTFP00000416</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>golden-sgf-poupanca-conservadora</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Golden SGF Poupança Conservadora</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PTFP00000424</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>golden-sgf-poupanca-dinamica</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Golden SGF Poupança Dinâmica</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PTFP00000382</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>golden-sgf-poupanca-equilibrada</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Golden SGF Poupança Equilibrada</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PTFP00000432</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>golden-sgf-poupanca-garantida</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Golden SGF Poupança Garantida</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>golden-sgf-reforma-conservadora</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Golden SGF Reforma Conservadora</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PTFP00000515</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>golden-sgf-reforma-dinamica</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Golden SGF Reforma Dinâmica</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PTFP00000879</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>golden-sgf-reforma-equilibrada</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Golden SGF Reforma Equilibrada</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>PTFP00000507</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>golden-sgf-reforma-garantida</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Golden SGF Reforma Garantida</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PTFP00000473</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>golden-sgf-top-gestores</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Golden SGF TOP GESTORES</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Golden SGF</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PTOPZEHM0017</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PTOPZAHM0003</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PTOPZBHM0002</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OPTIMIZE PPR</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PTOPZDHM0000</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Optimize LFO PPR</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Optimize LFO PPR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Optimize LFO PPR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sgf-stoik</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PPR SGF Stoik</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sgf-dr-financas</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SGF DR FINANÇAS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sgf-deco-proteste</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SGF PPR DECO PROTESTE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sgf-reforma-stoik</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SGF Reforma Stoik</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>sgf-square-acoes</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>SGF Square Ações</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>SGF</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>golden_sgf</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>historical</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>FP-PPR</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR/OICVM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PTSFFAHM0013</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1423,7 +3631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,17 +3891,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-306</t>
+          <t>biz-europa-valorizacao-oiavm-ppr-fundo-de-investimento-alter-329</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT PPR / OICVM - Categoria A</t>
+          <t>BIZ EUROPA VALORIZAÇÃO OIAVM/PPR - Categoria A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT</t>
+          <t>BIZ EUROPA VALORIZAÇÃO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1712,38 +3920,30 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>PTBKCAHM0000</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-307</t>
+          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT PPR / OICVM - Categoria B</t>
+          <t>BPI Reforma Global Equities PPR/OICVM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT</t>
+          <t>BPI Reforma Global</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1763,16 +3963,12 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>PTBKCAHM0000</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
@@ -1783,17 +3979,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-308</t>
+          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT PPR / OICVM - Categoria C</t>
+          <t>BPI Reforma Investimento PPR/OICVM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT</t>
+          <t>BPI Reforma Investimento</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1813,37 +4009,33 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>PTBKCAHM0000</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>biz-europa-valorizacao-oiavm-ppr-fundo-de-investimento-alter-329</t>
+          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BIZ EUROPA VALORIZAÇÃO OIAVM/PPR - Categoria A</t>
+          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIZ EUROPA VALORIZAÇÃO</t>
+          <t>BPI Reforma Obrigações</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1862,30 +4054,34 @@
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
+          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BPI Reforma Global Equities PPR/OICVM</t>
+          <t>BPI Reforma Valorização PPR/OICVM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BPI Reforma Global</t>
+          <t>BPI Reforma Valorização</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1905,33 +4101,33 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
+          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento PPR/OICVM</t>
+          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1951,33 +4147,33 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1.94</v>
+        <v>0.49</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
+          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
+          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1997,11 +4193,9 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
@@ -2013,17 +4207,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização PPR/OICVM</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2043,33 +4237,33 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>2.32</v>
+        <v>0.97</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2088,34 +4282,34 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
+      <c r="H14" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2134,34 +4328,34 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
+      <c r="H15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2180,34 +4374,34 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
+      <c r="H16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2227,16 +4421,12 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1.68</v>
+        <v>0.54</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
@@ -2247,17 +4437,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2277,16 +4467,12 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.26</v>
+        <v>0.47</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -2297,17 +4483,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
+          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
+          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BlueCrow Global Opportunities</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2327,37 +4513,37 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>PTBLWTHM0004</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
+          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
+          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>CAIXA AÇÕES LÍDERES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2377,37 +4563,35 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4</v>
-      </c>
+        <v>1.81</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTIXAEHM0006</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2427,14 +4611,14 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTIXAFHM0005</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2447,17 +4631,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2477,14 +4661,14 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTIXAFHM0005</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2497,17 +4681,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2527,14 +4711,14 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2.39</v>
+        <v>0.82</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTIXAFHM0005</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2547,17 +4731,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2577,14 +4761,14 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1.66</v>
+        <v>0.64</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTIXAFHM0005</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2597,17 +4781,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
+          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
+          <t>Caixa Arrojado PPR / OICVM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>Caixa Arrojado PPR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2627,16 +4811,12 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>PTYBCQLM0000</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
@@ -2647,17 +4827,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
+          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
+          <t>Caixa Defensivo PPR / OICVM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>Caixa Defensivo PPR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2677,7 +4857,7 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.49</v>
+        <v>1.13</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
@@ -2686,24 +4866,24 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
+          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
+          <t>Caixa Moderado PPR / OICVM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>Caixa Moderado PPR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2723,31 +4903,33 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>1.48</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
+          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
+          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2766,34 +4948,36 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2813,33 +4997,33 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2859,33 +5043,33 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I30" t="n">
-        <v>3</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>100</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2905,13 +5089,15 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.65</v>
+        <v>2.09</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2921,17 +5107,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2951,13 +5137,15 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.54</v>
+        <v>2.08</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>100</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2967,17 +5155,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2997,13 +5185,15 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.47</v>
+        <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3013,17 +5203,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3043,37 +5233,35 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>PTBLWTHM0004</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
+          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3093,14 +5281,12 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>PTIXAEHM0006</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
@@ -3111,17 +5297,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3141,37 +5327,37 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>2.08</v>
+        <v>0.16</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTOXCRHM0001</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3191,37 +5377,39 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1.9</v>
+        <v>0.76</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>100000</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3241,37 +5429,39 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>100000</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3291,37 +5481,39 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1.34</v>
+        <v>0.76</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>100000</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3341,35 +5533,39 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>100000</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3389,35 +5585,39 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>PTOYADHM0008</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>100000</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3437,35 +5637,39 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>PTOYAEHM0007</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>100000</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3485,37 +5689,39 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="I43" t="n">
         <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>PTOYAFHM0006</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>100000</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3535,37 +5741,37 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>1.02</v>
+        <v>0.16</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
+          <t>PTOXCTHM0009</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3585,37 +5791,39 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="I45" t="n">
         <v>4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>100000</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3635,37 +5843,39 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>PTOYAIHM0003</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>100000</v>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3685,37 +5895,39 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1.52</v>
+        <v>0.76</v>
       </c>
       <c r="I47" t="n">
         <v>4</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>PTOYAJHM0002</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>100000</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3735,37 +5947,39 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1.4</v>
+        <v>0.76</v>
       </c>
       <c r="I48" t="n">
         <v>4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>PTOYAKHM0009</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>100000</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3785,37 +5999,39 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="I49" t="n">
         <v>4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>PTOYALHM0008</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>100000</v>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3835,37 +6051,39 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="I50" t="n">
         <v>4</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>PTOYAMHM0007</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>100000</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR / OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3885,33 +6103,37 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>2.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR / OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3931,33 +6153,37 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR / OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3977,33 +6203,37 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I53" t="n">
         <v>4</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PTOYARHM0002</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4023,39 +6253,37 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>1.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I54" t="n">
         <v>4</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTYESALM0007</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>25</v>
-      </c>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4074,36 +6302,38 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTGNFHHM0002</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>5</v>
-      </c>
+          <t>PTOYATHM0000</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4123,33 +6353,37 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="n">
-        <v>100</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PTOYAUHM0007</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4169,33 +6403,37 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
-        <v>100</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PTOYAVHM0006</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4215,35 +6453,37 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>2.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>4</v>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>100</v>
-      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PTOYAWHM0005</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4263,35 +6503,37 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>2.08</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="n">
-        <v>100</v>
-      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PTOYAXHM0004</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4311,35 +6553,37 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>4</v>
       </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="n">
-        <v>100</v>
-      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PTOXS3HM0000</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4359,35 +6603,37 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="n">
-        <v>100</v>
-      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PTOXS4HM0009</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4407,33 +6653,37 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>1.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PTOXS5HM0008</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4452,38 +6702,32 @@
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
-        <v>2.04</v>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>5</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>PTOPZEHM0017</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4503,37 +6747,39 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>2.57</v>
+        <v>1.06</v>
       </c>
       <c r="I64" t="n">
         <v>4</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>2000</v>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4553,37 +6799,39 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>2.36</v>
+        <v>1.06</v>
       </c>
       <c r="I65" t="n">
         <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>2000</v>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4603,32 +6851,34 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="I66" t="n">
         <v>4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTOPZDHM0000</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>2000</v>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4653,17 +6903,19 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0.16</v>
+        <v>1.06</v>
       </c>
       <c r="I67" t="n">
         <v>4</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>2000</v>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -4673,12 +6925,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4703,18 +6955,18 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I68" t="n">
         <v>4</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYA2HM0007</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4725,12 +6977,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4755,18 +7007,18 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I69" t="n">
         <v>4</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYA3HM0006</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4777,12 +7029,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4807,18 +7059,18 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I70" t="n">
         <v>4</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYA4HM0005</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4829,12 +7081,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4859,18 +7111,18 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I71" t="n">
         <v>4</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
+          <t>PTOYA5HM0004</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4881,12 +7133,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4911,18 +7163,18 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I72" t="n">
         <v>4</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOYA6HM0003</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4933,12 +7185,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4963,18 +7215,18 @@
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I73" t="n">
         <v>4</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4985,12 +7237,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5015,18 +7267,18 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I74" t="n">
         <v>4</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5037,12 +7289,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5067,17 +7319,19 @@
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>0.16</v>
+        <v>1.06</v>
       </c>
       <c r="I75" t="n">
         <v>4</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>PTOXSOHM0006</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>2000</v>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5087,12 +7341,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5117,18 +7371,18 @@
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -5139,12 +7393,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5169,18 +7423,18 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I77" t="n">
         <v>4</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5191,12 +7445,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5221,18 +7475,18 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I78" t="n">
         <v>4</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -5243,12 +7497,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5273,18 +7527,18 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I79" t="n">
         <v>4</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -5295,12 +7549,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5325,18 +7579,18 @@
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="I80" t="n">
         <v>4</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -5347,17 +7601,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5377,19 +7631,17 @@
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5399,17 +7651,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5429,14 +7681,14 @@
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTYSAVLM0006</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,17 +7701,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5479,2102 +7731,18 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTYMCRLM0006</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>PTOYARHM0002</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I85" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>PTOYASHM0001</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>PTOYATHM0000</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I87" t="n">
-        <v>4</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>PTOYAUHM0007</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I88" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>PTOYAVHM0006</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I89" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>PTOYAWHM0005</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I90" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>PTOYAXHM0004</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I91" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>PTOXS3HM0000</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I92" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>PTOXS4HM0009</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I93" t="n">
-        <v>4</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I95" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>PTOXTBHM0000</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I96" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>PTOYAYHM0003</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I97" t="n">
-        <v>4</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>PTOYAZHM0002</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I98" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>PTOYA1HM0008</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I99" t="n">
-        <v>4</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>PTOYA2HM0007</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I100" t="n">
-        <v>4</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>PTOYA3HM0006</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I101" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>PTOYA4HM0005</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I102" t="n">
-        <v>4</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>PTOYA5HM0004</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I103" t="n">
-        <v>4</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>PTOYA6HM0003</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I104" t="n">
-        <v>4</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>PTOXSMHM0008</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I105" t="n">
-        <v>4</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>PTOXSNHM0007</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I106" t="n">
-        <v>4</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>PTOXSOHM0006</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I107" t="n">
-        <v>4</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>PTOXSPHM0005</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I108" t="n">
-        <v>4</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>PTOXS6HM0007</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I109" t="n">
-        <v>4</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>PTOXS7HM0006</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I110" t="n">
-        <v>4</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>PTOXS8HM0005</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I111" t="n">
-        <v>4</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Optimize LFO PPR</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I112" t="n">
-        <v>5</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>PTOPZUHM0009</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Optimize LFO PPR</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I113" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>PTOPZQHM0005</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
-        <v>500000</v>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Optimize LFO PPR</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="I114" t="n">
-        <v>5</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>PTOPZVHM0008</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I115" t="n">
-        <v>3</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>PTSXYXHM0003</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES PPR</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I116" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES PPR</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I117" t="n">
-        <v>3</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES PPR</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I118" t="n">
-        <v>3</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I119" t="n">
-        <v>4</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I120" t="n">
-        <v>4</v>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I121" t="n">
-        <v>4</v>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Santander Aforro PPR/OICVM</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Santander Aforro PPR</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I122" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>PTSFFAHM0013</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente FPR</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I123" t="n">
-        <v>3</v>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>PTYSAVLM0006</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I124" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -7920,12 +8088,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7933,7 +8101,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>2.51</v>
       </c>
@@ -7970,12 +8142,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7983,7 +8155,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>1.9</v>
       </c>
@@ -8020,12 +8196,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8033,7 +8209,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1.99</v>
       </c>
@@ -8301,7 +8481,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8309,7 +8489,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
@@ -8347,7 +8531,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8355,7 +8539,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
@@ -8393,7 +8581,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8401,7 +8589,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
@@ -8439,7 +8631,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8447,7 +8639,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>1.68</v>
       </c>
@@ -8489,7 +8685,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -8497,7 +8693,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>1.26</v>
       </c>
@@ -8539,7 +8739,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -8547,7 +8747,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>1.1</v>
       </c>
@@ -8589,7 +8793,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -8597,7 +8801,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>2.03</v>
       </c>
@@ -8639,7 +8847,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8647,7 +8855,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>1.44</v>
       </c>
@@ -8689,7 +8901,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8697,7 +8909,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>1.3</v>
       </c>
@@ -8739,7 +8955,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8747,7 +8963,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>2.39</v>
       </c>
@@ -8789,7 +9009,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8797,7 +9017,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>1.66</v>
       </c>
@@ -8839,7 +9063,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8847,7 +9071,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>1.56</v>
       </c>
@@ -9353,7 +9581,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9361,7 +9589,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>2.08</v>
       </c>
@@ -9403,7 +9635,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9411,7 +9643,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>1.9</v>
       </c>
@@ -9453,7 +9689,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -9461,7 +9697,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>1.52</v>
       </c>
@@ -9503,7 +9743,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -9511,7 +9751,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>1.34</v>
       </c>
@@ -9553,7 +9797,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -9561,7 +9805,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>1.83</v>
       </c>
@@ -9601,7 +9849,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9609,7 +9857,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>1.68</v>
       </c>
@@ -9649,7 +9901,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -9657,7 +9909,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>1.47</v>
       </c>
@@ -9897,7 +10153,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9905,7 +10161,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>1.52</v>
       </c>
@@ -9947,7 +10207,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9955,7 +10215,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>1.4</v>
       </c>
@@ -9997,7 +10261,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10005,7 +10269,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>1.13</v>
       </c>
@@ -10047,7 +10315,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10055,7 +10323,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>1.01</v>
       </c>
@@ -10259,7 +10531,9 @@
           <t>PTCUUBHM0004</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>250000</v>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10313,7 +10587,9 @@
           <t>PTCUUAHM0005</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>1000</v>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10343,7 +10619,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10351,7 +10627,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>1.25</v>
       </c>
@@ -11325,7 +11605,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11333,7 +11613,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>2.04</v>
       </c>
@@ -11375,7 +11659,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -11383,7 +11667,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>2.57</v>
       </c>
@@ -11425,7 +11713,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -11433,7 +11721,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>2.36</v>
       </c>
@@ -11475,7 +11767,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -11483,7 +11775,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H81" t="n">
         <v>1.81</v>
       </c>
@@ -13829,7 +14125,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -13837,7 +14133,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>2.19</v>
       </c>
@@ -13881,7 +14181,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -13889,7 +14189,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>1.11</v>
       </c>
@@ -13933,7 +14237,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -13941,7 +14245,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>2.47</v>
       </c>
@@ -14253,7 +14561,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14261,7 +14569,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>1.89</v>
       </c>
@@ -14303,7 +14615,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -14311,7 +14623,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>1.39</v>
       </c>
@@ -14353,7 +14669,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -14361,7 +14677,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>1.89</v>
       </c>
@@ -14403,7 +14723,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -14411,7 +14731,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>1.52</v>
       </c>
@@ -14453,7 +14777,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14461,7 +14785,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>1.39</v>
       </c>
@@ -14503,7 +14831,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -14511,7 +14839,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>1.44</v>
       </c>
@@ -14553,7 +14885,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -14561,7 +14893,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>0.88</v>
       </c>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,22 +483,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>invest-ar</t>
+          <t>abanca-ppr-oicvm-ciclo-de-vida-55-fundo-de-investimento-aber-304</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALVES RIBEIRO PPR / OICVM</t>
+          <t>ABANCA PPR/OICVM Ciclo de Vida +55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALVES RIBEIRO PPR</t>
+          <t>ABANCA PPR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,17 +517,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PTYINVIM0007</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>PTAFIYHM0012</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -537,22 +539,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-306</t>
+          <t>abanca-ppr-oicvm-ciclo-de-vida-34-fundo-de-investimento-aber-301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT PPR / OICVM - Categoria A</t>
+          <t>ABANCA PPR/OICVM Ciclo de Vida -34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT</t>
+          <t>ABANCA PPR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -567,46 +569,48 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.51</v>
+        <v>2.23</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PTBKCAHM0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>PTAFIUHM0016</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-307</t>
+          <t>abanca-ppr-oicvm-ciclo-de-vida-35-44-fundo-de-investimento-a-302</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT PPR / OICVM - Categoria B</t>
+          <t>ABANCA PPR/OICVM Ciclo de Vida 35-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT</t>
+          <t>ABANCA PPR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -621,46 +625,48 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PTBKCAHM0000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>PTAFIVHM0015</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-308</t>
+          <t>abanca-ppr-oicvm-ciclo-de-vida-45-54-fundo-de-investimento-a-303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT PPR / OICVM - Categoria C</t>
+          <t>ABANCA PPR/OICVM Ciclo de Vida 45-54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BANKINTER MEGA TT</t>
+          <t>ABANCA PPR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -675,46 +681,48 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PTBKCAHM0000</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>PTAFIWHM0014</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
+          <t>invest-ar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
+          <t>ALVES RIBEIRO PPR / OICVM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>ALVES RIBEIRO PPR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -729,42 +737,46 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTYINVIM0007</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
+          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-306</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
+          <t>BANKINTER MEGA TT PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BANKINTER MEGA TT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -782,11 +794,15 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTBKCAHM0000</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -799,22 +815,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
+          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-307</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
+          <t>BANKINTER MEGA TT PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BANKINTER MEGA TT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -832,11 +848,15 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTBKCAHM0000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -849,22 +869,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
+          <t>bankinter-mega-tt-ppr-oicvm-fundo-de-investimento-mobiliario-308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
+          <t>BANKINTER MEGA TT PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BANKINTER MEGA TT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -883,32 +903,32 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTBKCAHM0000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -936,12 +956,8 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>PTYBCPLM0001</t>
@@ -950,19 +966,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -990,12 +1006,8 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4</v>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>PTYBCPLM0001</t>
@@ -1004,19 +1016,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1044,33 +1056,29 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1099,14 +1107,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1119,12 +1127,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1153,14 +1161,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1173,12 +1181,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1207,14 +1215,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.39</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1227,12 +1235,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1261,14 +1269,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1281,12 +1289,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1315,14 +1323,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1335,17 +1343,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1365,18 +1373,18 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1389,17 +1397,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1419,18 +1427,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1443,17 +1451,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1473,18 +1481,18 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="I20" t="n">
         <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1497,17 +1505,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1527,18 +1535,18 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="I21" t="n">
         <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1551,17 +1559,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1585,35 +1593,37 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>2.08</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1637,35 +1647,37 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1689,35 +1701,37 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1741,14 +1755,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1761,17 +1775,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1795,37 +1809,35 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
-      </c>
+        <v>1.83</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1849,37 +1861,35 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4</v>
-      </c>
+        <v>1.68</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1903,42 +1913,40 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
+        <v>1.47</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>casa-inv-sg-founders</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Founders</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1953,48 +1961,46 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTCUUBHM0004</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>250000</v>
-      </c>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>casa-inv-sg-prime</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Prime</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2009,43 +2015,41 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTCUUAHM0005</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2065,23 +2069,21 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PTYESALM0007</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>25</v>
-      </c>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2091,22 +2093,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-plus</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Plus</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2116,47 +2118,51 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PTFP00000762</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-start</t>
+          <t>casa-inv-sg-founders</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Start</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR — Founders</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2166,47 +2172,53 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>1.45</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTFP00000861</t>
+          <t>PTCUUBHM0004</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>250000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-ativa</t>
+          <t>casa-inv-sg-prime</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Ativa</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR — Prime</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2216,43 +2228,53 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTFP00000416</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>PTCUUAHM0005</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-conservadora</t>
+          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Conservadora</t>
+          <t>GNB PPR/OICVM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2262,33 +2284,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTFP00000424</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>PTYESALM0007</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>25</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-dinamica</t>
+          <t>golden-sgf-etf-plus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Dinâmica</t>
+          <t>Golden SGF ETF Plus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2313,28 +2345,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTFP00000382</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>PTFP00000762</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>10000</v>
+      </c>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-equilibrada</t>
+          <t>golden-sgf-etf-start</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Equilibrada</t>
+          <t>Golden SGF ETF Start</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2359,28 +2395,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTFP00000432</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>PTFP00000861</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1500</v>
+      </c>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-garantida</t>
+          <t>golden-sgf-poupanca-ativa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Garantida</t>
+          <t>Golden SGF Poupança Ativa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2410,19 +2450,23 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PTFP00000416</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-conservadora</t>
+          <t>golden-sgf-poupanca-conservadora</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Conservadora</t>
+          <t>Golden SGF Poupança Conservadora</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2454,7 +2498,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTFP00000515</t>
+          <t>PTFP00000424</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2463,12 +2507,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-dinamica</t>
+          <t>golden-sgf-poupanca-dinamica</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Dinâmica</t>
+          <t>Golden SGF Poupança Dinâmica</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2500,7 +2544,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTFP00000879</t>
+          <t>PTFP00000382</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2509,12 +2553,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-equilibrada</t>
+          <t>golden-sgf-poupanca-equilibrada</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Equilibrada</t>
+          <t>Golden SGF Poupança Equilibrada</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2546,7 +2590,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTFP00000507</t>
+          <t>PTFP00000432</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2555,12 +2599,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-garantida</t>
+          <t>golden-sgf-poupanca-garantida</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Garantida</t>
+          <t>Golden SGF Poupança Garantida</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2590,23 +2634,19 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>PTFP00000473</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>golden-sgf-top-gestores</t>
+          <t>golden-sgf-reforma-conservadora</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Golden SGF TOP GESTORES</t>
+          <t>Golden SGF Reforma Conservadora</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2636,29 +2676,33 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PTFP00000515</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>golden-sgf-reforma-dinamica</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>Golden SGF Reforma Dinâmica</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2668,51 +2712,43 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I44" t="n">
-        <v>5</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOPZEHM0017</t>
+          <t>PTFP00000879</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>golden-sgf-reforma-equilibrada</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>Golden SGF Reforma Equilibrada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2722,51 +2758,43 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
+          <t>PTFP00000507</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>golden-sgf-reforma-garantida</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>Golden SGF Reforma Garantida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2776,51 +2804,43 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I46" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
+          <t>PTFP00000473</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>golden-sgf-top-gestores</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>Golden SGF TOP GESTORES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2830,46 +2850,34 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>PTOPZDHM0000</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2893,19 +2901,17 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="I48" t="n">
         <v>5</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOPZUHM0009</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>10000</v>
-      </c>
+          <t>PTOPZEHM0017</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2915,17 +2921,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2949,19 +2955,17 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.11</v>
+        <v>2.57</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTOPZQHM0005</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>500000</v>
-      </c>
+          <t>PTOPZAHM0003</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2971,17 +2975,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3005,19 +3009,17 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTOPZVHM0008</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTOPZBHM0002</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3027,22 +3029,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3052,43 +3054,51 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
+          <t>PTOPZDHM0000</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3098,39 +3108,53 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3140,43 +3164,53 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTFP00000770</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3186,29 +3220,43 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sgf-square-acoes</t>
+          <t>sgf-stoik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SGF Square Ações</t>
+          <t>PPR SGF Stoik</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3238,29 +3286,33 @@
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+          <t>sgf-dr-financas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+          <t>SGF DR FINANÇAS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3270,51 +3322,39 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+          <t>sgf-deco-proteste</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+          <t>SGF PPR DECO PROTESTE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3324,51 +3364,43 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
+          <t>PTFP00000770</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+          <t>sgf-reforma-stoik</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+          <t>SGF Reforma Stoik</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3378,51 +3410,39 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
+          <t>sgf-square-acoes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+          <t>SGF Square Ações</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3432,46 +3452,34 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SIXTY DEGREES PPR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3495,37 +3503,37 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
+          <t>PTSXYAHM0000</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SIXTY DEGREES PPR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3549,37 +3557,37 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
+          <t>PTSXYAHM0000</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Santander Aforro PPR/OICVM</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santander Aforro PPR</t>
+          <t>SIXTY DEGREES PPR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3599,22 +3607,238 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.88</v>
+        <v>1.89</v>
       </c>
       <c r="I62" t="n">
         <v>3</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTSFFAHM0013</t>
+          <t>PTSXYAHM0000</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR/OICVM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PTSFFAHM0013</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
@@ -3631,7 +3855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3699,17 +3923,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>abanca-ppr-oicvm-ciclo-de-vida-55-fundo-de-investimento-aber-304</t>
+          <t>biz-europa-valorizacao-oiavm-ppr-fundo-de-investimento-alter-329</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABANCA PPR/OICVM Ciclo de Vida +55</t>
+          <t>BIZ EUROPA VALORIZAÇÃO OIAVM/PPR - Categoria A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABANCA PPR</t>
+          <t>BIZ EUROPA VALORIZAÇÃO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3728,36 +3952,30 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>100</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>abanca-ppr-oicvm-ciclo-de-vida-34-fundo-de-investimento-aber-301</t>
+          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABANCA PPR/OICVM Ciclo de Vida -34</t>
+          <t>BPI Reforma Global Equities PPR/OICVM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABANCA PPR</t>
+          <t>BPI Reforma Global</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3777,35 +3995,33 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>100</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>abanca-ppr-oicvm-ciclo-de-vida-35-44-fundo-de-investimento-a-302</t>
+          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ABANCA PPR/OICVM Ciclo de Vida 35-44</t>
+          <t>BPI Reforma Investimento PPR/OICVM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABANCA PPR</t>
+          <t>BPI Reforma Investimento</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3825,15 +4041,13 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>100</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3843,17 +4057,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>abanca-ppr-oicvm-ciclo-de-vida-45-54-fundo-de-investimento-a-303</t>
+          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ABANCA PPR/OICVM Ciclo de Vida 45-54</t>
+          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABANCA PPR</t>
+          <t>BPI Reforma Obrigações</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3873,35 +4087,33 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1.77</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>100</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>biz-europa-valorizacao-oiavm-ppr-fundo-de-investimento-alter-329</t>
+          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIZ EUROPA VALORIZAÇÃO OIAVM/PPR - Categoria A</t>
+          <t>BPI Reforma Valorização PPR/OICVM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ EUROPA VALORIZAÇÃO</t>
+          <t>BPI Reforma Valorização</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3920,30 +4132,34 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
+          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BPI Reforma Global Equities PPR/OICVM</t>
+          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BPI Reforma Global</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3963,33 +4179,33 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>2.21</v>
+        <v>0.49</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
+          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento PPR/OICVM</t>
+          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4009,33 +4225,31 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4055,7 +4269,7 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.16</v>
+        <v>0.97</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -4071,17 +4285,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização PPR/OICVM</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4101,33 +4315,33 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>0.64</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4147,7 +4361,7 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.49</v>
+        <v>0.68</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
@@ -4163,17 +4377,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4193,31 +4407,33 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>0.65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4237,7 +4453,7 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>0.54</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
@@ -4246,24 +4462,24 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4283,7 +4499,7 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -4292,24 +4508,24 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
+          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
+          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>BlueCrow Global Opportunities</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4329,33 +4545,37 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PTBLWTHM0004</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
+          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
+          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>CAIXA AÇÕES LÍDERES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4375,33 +4595,35 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1.81</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PTIXAEHM0006</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4421,12 +4643,16 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.54</v>
+        <v>1.13</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
@@ -4437,17 +4663,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4467,12 +4693,16 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -4483,17 +4713,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4513,37 +4743,37 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTBLWTHM0004</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4563,35 +4793,37 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>0.64</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTIXAEHM0006</t>
+          <t>PTIXAFHM0005</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
+          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
+          <t>Caixa Arrojado PPR / OICVM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>Caixa Arrojado PPR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4611,16 +4843,12 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1.13</v>
+        <v>2.02</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
@@ -4631,17 +4859,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
+          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
+          <t>Caixa Defensivo PPR / OICVM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>Caixa Defensivo PPR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4661,16 +4889,12 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
@@ -4681,17 +4905,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
+          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
+          <t>Caixa Moderado PPR / OICVM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>Caixa Moderado PPR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4711,16 +4935,12 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
@@ -4731,17 +4951,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
+          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
+          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4760,38 +4980,36 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR / OICVM</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4811,33 +5029,33 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR / OICVM</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4857,33 +5075,33 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>100</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR / OICVM</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4903,13 +5121,15 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1.48</v>
+        <v>2.09</v>
       </c>
       <c r="I27" t="n">
         <v>4</v>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4919,17 +5139,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4948,36 +5168,36 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>PTGNFHHM0002</t>
-        </is>
-      </c>
+      <c r="H28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4997,33 +5217,35 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
         <v>100</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5043,33 +5265,35 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>100</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
+          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5089,35 +5313,33 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>100</v>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5137,35 +5359,37 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>2.08</v>
+        <v>0.16</v>
       </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>100</v>
-      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5185,35 +5409,39 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I33" t="n">
         <v>4</v>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5233,35 +5461,39 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I34" t="n">
         <v>4</v>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5281,28 +5513,34 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>100000</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5327,17 +5565,19 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I36" t="n">
         <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>100000</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5347,12 +5587,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5384,7 +5624,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYADHM0008</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -5399,12 +5639,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5436,7 +5676,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYAEHM0007</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -5451,12 +5691,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5488,7 +5728,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYAFHM0006</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -5503,12 +5743,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5533,19 +5773,17 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0.76</v>
+        <v>0.16</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXCTHM0009</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5555,12 +5793,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5592,7 +5830,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOXCUHM0006</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -5607,12 +5845,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5644,7 +5882,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
+          <t>PTOYAIHM0003</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -5659,12 +5897,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5696,7 +5934,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
+          <t>PTOYAJHM0002</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -5711,12 +5949,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5741,17 +5979,19 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>PTOYAKHM0009</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>100000</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5761,12 +6001,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5798,7 +6038,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
+          <t>PTOYALHM0008</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -5813,12 +6053,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5850,7 +6090,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
+          <t>PTOYAMHM0007</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -5865,12 +6105,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5895,19 +6135,17 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I47" t="n">
         <v>4</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5917,12 +6155,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5947,19 +6185,17 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I48" t="n">
         <v>4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5969,12 +6205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5999,19 +6235,17 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
         <v>4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYARHM0002</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6021,12 +6255,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6051,19 +6285,17 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I50" t="n">
         <v>4</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6073,12 +6305,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6110,7 +6342,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTOYATHM0000</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6123,12 +6355,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6160,7 +6392,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTOYAUHM0007</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -6173,12 +6405,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6210,7 +6442,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTOYARHM0002</t>
+          <t>PTOYAVHM0006</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6223,12 +6455,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6260,7 +6492,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTOYASHM0001</t>
+          <t>PTOYAWHM0005</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6273,12 +6505,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6310,7 +6542,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTOYATHM0000</t>
+          <t>PTOYAXHM0004</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -6323,12 +6555,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6360,7 +6592,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PTOYAUHM0007</t>
+          <t>PTOXS3HM0000</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -6373,12 +6605,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6410,7 +6642,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTOYAVHM0006</t>
+          <t>PTOXS4HM0009</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -6423,12 +6655,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6460,7 +6692,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTOYAWHM0005</t>
+          <t>PTOXS5HM0008</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -6473,12 +6705,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6502,17 +6734,11 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>PTOYAXHM0004</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
@@ -6523,12 +6749,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6553,17 +6779,19 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I60" t="n">
         <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTOXS3HM0000</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>2000</v>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6573,12 +6801,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6603,17 +6831,19 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTOXS4HM0009</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>2000</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6623,12 +6853,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6653,17 +6883,19 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I62" t="n">
         <v>4</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>2000</v>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6673,12 +6905,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6702,12 +6934,20 @@
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I63" t="n">
         <v>4</v>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>2000</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6717,12 +6957,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6754,7 +6994,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTOXTBHM0000</t>
+          <t>PTOYA2HM0007</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -6769,12 +7009,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6806,7 +7046,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTOYAYHM0003</t>
+          <t>PTOYA3HM0006</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -6821,12 +7061,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6858,7 +7098,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTOYAZHM0002</t>
+          <t>PTOYA4HM0005</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -6873,12 +7113,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6910,7 +7150,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTOYA1HM0008</t>
+          <t>PTOYA5HM0004</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -6925,12 +7165,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6962,7 +7202,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PTOYA2HM0007</t>
+          <t>PTOYA6HM0003</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -6977,12 +7217,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7014,7 +7254,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PTOYA3HM0006</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -7029,12 +7269,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7066,7 +7306,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PTOYA4HM0005</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -7081,12 +7321,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7118,7 +7358,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTOYA5HM0004</t>
+          <t>PTOXSOHM0006</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -7133,12 +7373,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7170,7 +7410,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTOYA6HM0003</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -7185,12 +7425,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7222,7 +7462,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PTOXSMHM0008</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -7237,12 +7477,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7274,7 +7514,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PTOXSNHM0007</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -7289,12 +7529,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7326,7 +7566,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PTOXSOHM0006</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -7341,12 +7581,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7378,7 +7618,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>PTOXSPHM0005</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -7393,17 +7633,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7423,19 +7663,17 @@
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>PTOXS6HM0007</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7445,17 +7683,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7475,19 +7713,17 @@
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>PTOXS7HM0006</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7497,17 +7733,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7527,222 +7763,18 @@
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PTOXS8HM0005</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I80" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>PTSXYXHM0003</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente FPR</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I82" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>PTYSAVLM0006</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I83" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -7847,7 +7879,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -7855,14 +7887,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PTAFIYHM0012</t>
+        </is>
+      </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
@@ -7895,7 +7935,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7903,14 +7943,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2.23</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PTAFIUHM0016</t>
+        </is>
+      </c>
       <c r="K3" t="n">
         <v>100</v>
       </c>
@@ -7943,7 +7991,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7951,14 +7999,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>1.92</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PTAFIVHM0015</t>
+        </is>
+      </c>
       <c r="K4" t="n">
         <v>100</v>
       </c>
@@ -7991,7 +8047,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7999,14 +8055,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>1.77</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PTAFIWHM0014</t>
+        </is>
+      </c>
       <c r="K5" t="n">
         <v>100</v>
       </c>
@@ -14571,7 +14635,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -14625,7 +14689,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -14679,7 +14743,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H138" t="n">

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
+          <t>biz-europa-valorizacao-oiavm-ppr-fundo-de-investimento-alter-329</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
+          <t>BIZ EUROPA VALORIZAÇÃO OIAVM/PPR - Categoria A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BIZ EUROPA VALORIZAÇÃO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -953,32 +953,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>PTBZSKHM0003</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1023,12 +1025,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1073,12 +1075,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1106,12 +1108,8 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>PTYBCPLM0001</t>
@@ -1120,19 +1118,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1161,7 +1159,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
@@ -1181,12 +1179,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1215,7 +1213,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -1235,12 +1233,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1269,14 +1267,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2.03</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1289,12 +1287,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1323,7 +1321,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="I17" t="n">
         <v>4</v>
@@ -1343,12 +1341,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1377,7 +1375,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
@@ -1397,12 +1395,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1431,14 +1429,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.39</v>
+        <v>1.3</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1451,12 +1449,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1485,7 +1483,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.66</v>
+        <v>2.39</v>
       </c>
       <c r="I20" t="n">
         <v>5</v>
@@ -1505,12 +1503,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1539,7 +1537,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="I21" t="n">
         <v>5</v>
@@ -1559,17 +1557,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1589,18 +1587,18 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="I22" t="n">
         <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1613,17 +1611,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
+          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
+          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1643,41 +1641,41 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.9</v>
+        <v>0.49</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTBKCCHM0008</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
+          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
+          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1697,41 +1695,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTBKCKHM0008</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1751,41 +1747,41 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.34</v>
+        <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCDLM0005</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1805,39 +1801,41 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>0.64</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTYBCDLM0005</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1857,39 +1855,41 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>0.68</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTYBCDLM0005</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1909,39 +1909,41 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>0.65</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTYBCJHM0013</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1961,18 +1963,18 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.52</v>
+        <v>0.54</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTYBCJHM0013</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1985,17 +1987,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2015,18 +2017,18 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.4</v>
+        <v>0.47</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTYBCJHM0013</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2039,17 +2041,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
+          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
+          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA AÇÕES LÍDERES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2073,37 +2075,37 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4</v>
-      </c>
+        <v>1.81</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>PTCXGUHM0006</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2127,14 +2129,14 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2147,22 +2149,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>casa-inv-sg-founders</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Founders</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2177,48 +2179,46 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTCUUBHM0004</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>250000</v>
-      </c>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>casa-inv-sg-prime</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Prime</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2233,43 +2233,41 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTCUUAHM0005</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2289,23 +2287,21 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTYESALM0007</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>25</v>
-      </c>
+          <t>PTCXGBHM0017</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2315,22 +2311,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-plus</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Plus</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2340,47 +2336,49 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.75</v>
+        <v>1.83</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTFP00000762</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-start</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Start</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2390,47 +2388,49 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>1.68</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTFP00000861</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>PTCXGWHM0020</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-ativa</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Ativa</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2440,43 +2440,49 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1.47</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTFP00000416</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-conservadora</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Conservadora</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2486,43 +2492,51 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTFP00000424</t>
+          <t>PTCXGMHM0014</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-dinamica</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Dinâmica</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2532,43 +2546,51 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTFP00000382</t>
+          <t>PTCXGMHM0014</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-equilibrada</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Equilibrada</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2578,43 +2600,51 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTFP00000432</t>
+          <t>PTCXGMHM0014</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-garantida</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Garantida</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2624,39 +2654,51 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PTCXGMHM0014</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-conservadora</t>
+          <t>casa-inv-sg-founders</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Conservadora</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Founders</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2666,43 +2708,53 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTFP00000515</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+          <t>PTCUUBHM0004</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-dinamica</t>
+          <t>casa-inv-sg-prime</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Dinâmica</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Prime</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2712,43 +2764,53 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6</v>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTFP00000879</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>PTCUUAHM0005</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-equilibrada</t>
+          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Equilibrada</t>
+          <t>GNB PPR/OICVM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2758,33 +2820,43 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTFP00000507</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+          <t>PTYESALM0007</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>25</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-garantida</t>
+          <t>golden-sgf-etf-plus</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Garantida</t>
+          <t>Golden SGF ETF Plus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2809,28 +2881,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTFP00000473</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>PTFP00000762</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>10000</v>
+      </c>
       <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>golden-sgf-top-gestores</t>
+          <t>golden-sgf-etf-start</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Golden SGF TOP GESTORES</t>
+          <t>Golden SGF ETF Start</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2855,34 +2931,42 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>PTFP00000861</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1500</v>
+      </c>
       <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>golden-sgf-poupanca-ativa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>Golden SGF Poupança Ativa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2892,51 +2976,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOPZEHM0017</t>
+          <t>PTFP00000416</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>golden-sgf-poupanca-conservadora</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>Golden SGF Poupança Conservadora</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2946,51 +3022,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
+          <t>PTFP00000424</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>golden-sgf-poupanca-dinamica</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>Golden SGF Poupança Dinâmica</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3000,51 +3068,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I50" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
+          <t>PTFP00000382</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>golden-sgf-poupanca-equilibrada</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>Golden SGF Poupança Equilibrada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3054,51 +3114,43 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTOPZDHM0000</t>
+          <t>PTFP00000432</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+          <t>golden-sgf-poupanca-garantida</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+          <t>Golden SGF Poupança Garantida</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3108,53 +3160,39 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="I52" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>PTOPZUHM0009</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+          <t>golden-sgf-reforma-conservadora</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+          <t>Golden SGF Reforma Conservadora</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3164,53 +3202,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTOPZQHM0005</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>500000</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000515</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+          <t>golden-sgf-reforma-dinamica</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+          <t>Golden SGF Reforma Dinâmica</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3220,48 +3248,38 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="I54" t="n">
-        <v>5</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTOPZVHM0008</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000879</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>golden-sgf-reforma-equilibrada</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>Golden SGF Reforma Equilibrada</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3288,7 +3306,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
+          <t>PTFP00000507</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3297,17 +3315,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>golden-sgf-reforma-garantida</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>Golden SGF Reforma Garantida</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3332,24 +3350,28 @@
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PTFP00000473</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>golden-sgf-top-gestores</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>Golden SGF TOP GESTORES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3374,33 +3396,29 @@
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>PTFP00000770</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3410,39 +3428,51 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PTOPZAHM0003</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sgf-square-acoes</t>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SGF Square Ações</t>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3452,34 +3482,46 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PTOPZBHM0002</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3499,41 +3541,41 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
+          <t>PTOPZDHM0000</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3553,41 +3595,43 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>10000</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3607,41 +3651,43 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>500000</v>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3661,21 +3707,23 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.52</v>
+        <v>2.47</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1000</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3685,22 +3733,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>sgf-stoik</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>PPR SGF Stoik</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3710,51 +3758,43 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
+          <t>PTFP00000390</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
+          <t>sgf-dr-financas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
+          <t>SGF DR FINANÇAS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3764,81 +3804,415 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>sgf-deco-proteste</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SGF PPR DECO PROTESTE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sgf-reforma-stoik</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SGF Reforma Stoik</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sgf-square-acoes</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SGF Square Ações</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Santander Aforro PPR/OICVM</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Santander Aforro PPR</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>historical</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="H73" t="n">
         <v>0.88</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I73" t="n">
         <v>3</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>PTSFFAHM0013</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
@@ -3855,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3923,17 +4297,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>biz-europa-valorizacao-oiavm-ppr-fundo-de-investimento-alter-329</t>
+          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BIZ EUROPA VALORIZAÇÃO OIAVM/PPR - Categoria A</t>
+          <t>BPI Reforma Global Equities PPR/OICVM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BIZ EUROPA VALORIZAÇÃO</t>
+          <t>BPI Reforma Global</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3952,30 +4326,34 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
+          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BPI Reforma Global Equities PPR/OICVM</t>
+          <t>BPI Reforma Investimento PPR/OICVM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BPI Reforma Global</t>
+          <t>BPI Reforma Investimento</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3995,33 +4373,33 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
+          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento PPR/OICVM</t>
+          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento</t>
+          <t>BPI Reforma Obrigações</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4041,33 +4419,33 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.94</v>
+        <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
+          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
+          <t>BPI Reforma Valorização PPR/OICVM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações</t>
+          <t>BPI Reforma Valorização</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4087,33 +4465,33 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1.16</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
+          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização PPR/OICVM</t>
+          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização</t>
+          <t>BlueCrow Global Opportunities</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4133,33 +4511,37 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PTBLWTHM0004</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4179,33 +4561,37 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.49</v>
+        <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4225,31 +4611,37 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>1.02</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4269,33 +4661,37 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4318,30 +4714,34 @@
         <v>0.64</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PTIXAFHM0005</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
+          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
+          <t>Caixa Arrojado PPR / OICVM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>Caixa Arrojado PPR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4361,33 +4761,33 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.68</v>
+        <v>2.02</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
+          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
+          <t>Caixa Defensivo PPR / OICVM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>Caixa Defensivo PPR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4407,7 +4807,7 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -4423,17 +4823,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
+          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
+          <t>Caixa Moderado PPR / OICVM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>Caixa Moderado PPR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4453,10 +4853,10 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.54</v>
+        <v>1.48</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -4469,17 +4869,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
+          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
+          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4498,34 +4898,36 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4545,37 +4947,33 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.02</v>
+        <v>1.75</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>PTBLWTHM0004</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4595,15 +4993,13 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>PTIXAEHM0006</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4613,17 +5009,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4643,17 +5039,15 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1.13</v>
+        <v>2.09</v>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4663,17 +5057,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4693,17 +5087,15 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4713,17 +5105,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4743,17 +5135,15 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.82</v>
+        <v>1.6</v>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4763,17 +5153,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4793,17 +5183,15 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.64</v>
+        <v>1.6</v>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4813,17 +5201,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
+          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR / OICVM</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4843,33 +5231,33 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR / OICVM</t>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4889,12 +5277,16 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1.13</v>
+        <v>2.04</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PTOPZEHM0017</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
@@ -4905,17 +5297,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR / OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4935,33 +5327,37 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.48</v>
+        <v>0.16</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4980,36 +5376,40 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTGNFHHM0002</t>
+          <t>PTOXCSHM0000</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>100000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5029,33 +5429,39 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5075,33 +5481,39 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5121,35 +5533,39 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>2.09</v>
+        <v>0.76</v>
       </c>
       <c r="I27" t="n">
         <v>4</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5169,35 +5585,39 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>2.08</v>
+        <v>0.76</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PTOYADHM0008</t>
+        </is>
+      </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5217,35 +5637,39 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I29" t="n">
         <v>4</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PTOYAEHM0007</t>
+        </is>
+      </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5265,35 +5689,39 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I30" t="n">
         <v>4</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PTOYAFHM0006</t>
+        </is>
+      </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5313,28 +5741,32 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1.6</v>
+        <v>0.16</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PTOXCTHM0009</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5359,17 +5791,19 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>100000</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5379,12 +5813,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5416,7 +5850,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYAIHM0003</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -5431,12 +5865,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5468,7 +5902,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYAJHM0002</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -5483,12 +5917,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5520,7 +5954,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYAKHM0009</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -5535,12 +5969,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5572,7 +6006,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
+          <t>PTOYALHM0008</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -5587,12 +6021,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5624,7 +6058,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOYAMHM0007</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -5639,12 +6073,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5669,19 +6103,17 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>4</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5691,12 +6123,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5721,19 +6153,17 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5743,12 +6173,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5773,14 +6203,14 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
+          <t>PTOYARHM0002</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5793,12 +6223,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5823,19 +6253,17 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>4</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5845,12 +6273,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5875,19 +6303,17 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYATHM0000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5897,12 +6323,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5927,19 +6353,17 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAUHM0007</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5949,12 +6373,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5979,19 +6403,17 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAVHM0006</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6001,12 +6423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6031,19 +6453,17 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAWHM0005</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6053,12 +6473,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6083,19 +6503,17 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAXHM0004</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6105,12 +6523,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6142,7 +6560,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTOXS3HM0000</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -6155,12 +6573,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6192,7 +6610,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTOXS4HM0009</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6205,12 +6623,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6242,7 +6660,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTOYARHM0002</t>
+          <t>PTOXS5HM0008</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -6255,12 +6673,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6284,17 +6702,11 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>4</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>PTOYASHM0001</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
@@ -6305,12 +6717,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6335,17 +6747,19 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I51" t="n">
         <v>4</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTOYATHM0000</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>2000</v>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6355,12 +6769,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6385,17 +6799,19 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I52" t="n">
         <v>4</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTOYAUHM0007</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>2000</v>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6405,12 +6821,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6435,17 +6851,19 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I53" t="n">
         <v>4</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTOYAVHM0006</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>2000</v>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6455,12 +6873,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6485,17 +6903,19 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I54" t="n">
         <v>4</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTOYAWHM0005</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>2000</v>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6505,12 +6925,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6535,17 +6955,19 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I55" t="n">
         <v>4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTOYAXHM0004</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>PTOYA2HM0007</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>2000</v>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6555,12 +6977,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6585,17 +7007,19 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I56" t="n">
         <v>4</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PTOXS3HM0000</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>PTOYA3HM0006</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>2000</v>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6605,12 +7029,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6635,17 +7059,19 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I57" t="n">
         <v>4</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTOXS4HM0009</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>PTOYA4HM0005</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>2000</v>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6655,12 +7081,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6685,17 +7111,19 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I58" t="n">
         <v>4</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>PTOYA5HM0004</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>2000</v>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6705,12 +7133,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6734,12 +7162,20 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PTOYA6HM0003</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>2000</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6749,12 +7185,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6786,7 +7222,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTOXTBHM0000</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -6801,12 +7237,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6838,7 +7274,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTOYAYHM0003</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -6853,12 +7289,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6890,7 +7326,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTOYAZHM0002</t>
+          <t>PTOXSOHM0006</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -6905,12 +7341,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6942,7 +7378,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTOYA1HM0008</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -6957,12 +7393,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6994,7 +7430,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTOYA2HM0007</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -7009,12 +7445,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7046,7 +7482,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTOYA3HM0006</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -7061,12 +7497,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7098,7 +7534,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTOYA4HM0005</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -7113,12 +7549,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7150,7 +7586,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTOYA5HM0004</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -7165,17 +7601,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7195,19 +7631,17 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PTOYA6HM0003</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7217,17 +7651,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SMART INVEST PPR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7247,39 +7681,33 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1.06</v>
+        <v>1.39</v>
       </c>
       <c r="I69" t="n">
         <v>4</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>PTOXSMHM0008</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>2000</v>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SMART INVEST PPR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7299,39 +7727,33 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="I70" t="n">
         <v>4</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>PTOXSNHM0007</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>2000</v>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7351,19 +7773,17 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTOXSOHM0006</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7373,17 +7793,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7403,378 +7823,18 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTOXSPHM0005</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I73" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>PTOXS6HM0007</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I74" t="n">
-        <v>4</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>PTOXS7HM0006</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>PTOXS8HM0005</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I76" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I77" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>PTSXYXHM0003</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente FPR</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I78" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>PTYSAVLM0006</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I79" t="n">
-        <v>3</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -8319,7 +8379,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -8327,11 +8387,21 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PTBZSKHM0003</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -9181,7 +9251,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9189,14 +9259,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>0.49</v>
       </c>
       <c r="I27" t="n">
         <v>3</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PTBKCCHM0008</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
@@ -9227,7 +9305,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9235,12 +9313,20 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>0.62</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PTBKCKHM0008</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
@@ -9271,7 +9357,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9279,14 +9365,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PTYBCDLM0005</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
@@ -9317,7 +9411,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9325,14 +9419,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>0.64</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PTYBCDLM0005</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
@@ -9363,7 +9465,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9371,14 +9473,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>0.68</v>
       </c>
       <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PTYBCDLM0005</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
@@ -9409,7 +9519,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9417,14 +9527,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>0.65</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PTYBCJHM0013</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
@@ -9455,7 +9573,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9463,14 +9581,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>0.54</v>
       </c>
       <c r="I33" t="n">
         <v>3</v>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PTYBCJHM0013</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
@@ -9501,7 +9627,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9509,14 +9635,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>0.47</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PTYBCJHM0013</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
@@ -9597,7 +9731,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9605,17 +9739,23 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>1.81</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTIXAEHM0006</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>PTCXGUHM0006</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10556,7 +10696,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Founders</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Founders</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10612,7 +10752,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR — Prime</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Prime</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -10693,7 +10833,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -11669,7 +11809,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11677,11 +11817,7 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2.04</v>
       </c>
@@ -14841,7 +14977,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14849,22 +14985,14 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
         <v>4</v>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
@@ -14895,7 +15023,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -14903,22 +15031,14 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>1.44</v>
       </c>
       <c r="I141" t="n">
         <v>4</v>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2885,9 +2885,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
+        <v>0.83</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4</v>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>PTFP00000762</t>
@@ -2935,9 +2937,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4</v>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>PTFP00000861</t>
@@ -2984,14 +2988,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4</v>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>PTFP00000416</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>1500</v>
+      </c>
       <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3030,14 +3040,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>PTFP00000424</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>1500</v>
+      </c>
       <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3076,14 +3092,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>PTFP00000382</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>1500</v>
+      </c>
       <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3122,14 +3144,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>PTFP00000432</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>1500</v>
+      </c>
       <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3168,10 +3196,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PTFP00000408</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1500</v>
+      </c>
       <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3210,14 +3248,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>PTFP00000515</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>1500</v>
+      </c>
       <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3256,14 +3300,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>PTFP00000879</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>1500</v>
+      </c>
       <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3302,14 +3352,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>PTFP00000507</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>1500</v>
+      </c>
       <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3348,14 +3404,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>PTFP00000473</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>1500</v>
+      </c>
       <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3394,21 +3456,31 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PTFP00000457</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1500</v>
+      </c>
       <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3437,14 +3509,14 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
+          <t>PTOPZEHM0017</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3457,12 +3529,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3491,14 +3563,14 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="I59" t="n">
         <v>4</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
+          <t>PTOPZAHM0003</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -3511,12 +3583,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3545,14 +3617,14 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.81</v>
+        <v>2.36</v>
       </c>
       <c r="I60" t="n">
         <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTOPZDHM0000</t>
+          <t>PTOPZBHM0002</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3565,17 +3637,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3599,19 +3671,17 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTOPZUHM0009</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>10000</v>
-      </c>
+          <t>PTOPZDHM0000</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3621,12 +3691,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3655,18 +3725,18 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.11</v>
+        <v>2.19</v>
       </c>
       <c r="I62" t="n">
         <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTOPZQHM0005</t>
+          <t>PTOPZUHM0009</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>500000</v>
+        <v>10000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3677,12 +3747,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3711,18 +3781,18 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.47</v>
+        <v>1.11</v>
       </c>
       <c r="I63" t="n">
         <v>5</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTOPZVHM0008</t>
+          <t>PTOPZQHM0005</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>1000</v>
+        <v>500000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3733,22 +3803,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3758,33 +3828,43 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>sgf-stoik</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>PPR SGF Stoik</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3812,21 +3892,31 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1500</v>
+      </c>
       <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>sgf-dr-financas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>SGF DR FINANÇAS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3854,25 +3944,31 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTFP00000770</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>PTFP00000465</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1500</v>
+      </c>
       <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>sgf-deco-proteste</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>SGF PPR DECO PROTESTE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3900,21 +3996,31 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1500</v>
+      </c>
       <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sgf-square-acoes</t>
+          <t>sgf-reforma-stoik</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SGF Square Ações</t>
+          <t>SGF Reforma Stoik</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3945,28 +4051,30 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>1500</v>
+      </c>
       <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+          <t>sgf-square-acoes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+          <t>SGF Square Ações</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3976,41 +4084,35 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="I69" t="n">
         <v>3</v>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4039,7 +4141,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="I70" t="n">
         <v>3</v>
@@ -4059,12 +4161,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4093,7 +4195,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -4113,17 +4215,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SIXTY DEGREES PPR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4147,37 +4249,37 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
+          <t>PTSXYAHM0000</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Santander Aforro PPR/OICVM</t>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Santander Aforro PPR</t>
+          <t>SMART INVEST PPR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4197,22 +4299,76 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.88</v>
+        <v>1.39</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PTSFFAHM0013</t>
+          <t>PTARMIHM0004</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR/OICVM</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PTSFFAHM0013</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
@@ -4229,7 +4385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5247,17 +5403,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5277,32 +5433,32 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>2.04</v>
+        <v>0.16</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTOPZEHM0017</t>
+          <t>PTOXCRHM0001</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5327,17 +5483,19 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>100000</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5347,12 +5505,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5384,7 +5542,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYAAHM0001</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -5399,12 +5557,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5436,7 +5594,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYABHM0000</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -5451,12 +5609,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5488,7 +5646,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYACHM0009</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -5503,12 +5661,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5540,7 +5698,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
+          <t>PTOYADHM0008</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -5555,12 +5713,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5592,7 +5750,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOYAEHM0007</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -5607,12 +5765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5644,7 +5802,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
+          <t>PTOYAFHM0006</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -5659,12 +5817,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5689,19 +5847,17 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.76</v>
+        <v>0.16</v>
       </c>
       <c r="I30" t="n">
         <v>4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXCTHM0009</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5711,12 +5867,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5741,17 +5897,19 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>100000</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5761,12 +5919,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5798,7 +5956,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
+          <t>PTOYAIHM0003</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -5813,12 +5971,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5850,7 +6008,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
+          <t>PTOYAJHM0002</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -5865,12 +6023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5902,7 +6060,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
+          <t>PTOYAKHM0009</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -5917,12 +6075,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5954,7 +6112,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
+          <t>PTOYALHM0008</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -5969,12 +6127,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6006,7 +6164,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
+          <t>PTOYAMHM0007</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6021,12 +6179,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6051,19 +6209,17 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>4</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6073,12 +6229,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6110,7 +6266,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTOYAQHM0003</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -6123,12 +6279,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6160,7 +6316,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTOYARHM0002</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -6173,12 +6329,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6210,7 +6366,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTOYARHM0002</t>
+          <t>PTOYASHM0001</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -6223,12 +6379,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6260,7 +6416,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTOYASHM0001</t>
+          <t>PTOYATHM0000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -6273,12 +6429,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6310,7 +6466,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTOYATHM0000</t>
+          <t>PTOYAUHM0007</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -6323,12 +6479,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6360,7 +6516,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTOYAUHM0007</t>
+          <t>PTOYAVHM0006</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -6373,12 +6529,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6410,7 +6566,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOYAVHM0006</t>
+          <t>PTOYAWHM0005</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -6423,12 +6579,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6460,7 +6616,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOYAWHM0005</t>
+          <t>PTOYAXHM0004</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -6473,12 +6629,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6510,7 +6666,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOYAXHM0004</t>
+          <t>PTOXS3HM0000</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -6523,12 +6679,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6560,7 +6716,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTOXS3HM0000</t>
+          <t>PTOXS4HM0009</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -6573,12 +6729,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6610,7 +6766,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOXS4HM0009</t>
+          <t>PTOXS5HM0008</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6623,12 +6779,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6652,17 +6808,11 @@
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>4</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
@@ -6673,12 +6823,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6702,12 +6852,20 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I50" t="n">
         <v>4</v>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>2000</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6717,12 +6875,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6754,7 +6912,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTOXTBHM0000</t>
+          <t>PTOYAYHM0003</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -6769,12 +6927,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6806,7 +6964,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTOYAYHM0003</t>
+          <t>PTOYAZHM0002</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -6821,12 +6979,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6858,7 +7016,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTOYAZHM0002</t>
+          <t>PTOYA1HM0008</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -6873,12 +7031,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6910,7 +7068,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTOYA1HM0008</t>
+          <t>PTOYA2HM0007</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -6925,12 +7083,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6962,7 +7120,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTOYA2HM0007</t>
+          <t>PTOYA3HM0006</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -6977,12 +7135,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7014,7 +7172,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PTOYA3HM0006</t>
+          <t>PTOYA4HM0005</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -7029,12 +7187,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7066,7 +7224,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTOYA4HM0005</t>
+          <t>PTOYA5HM0004</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -7081,12 +7239,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7118,7 +7276,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTOYA5HM0004</t>
+          <t>PTOYA6HM0003</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -7133,12 +7291,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7170,7 +7328,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PTOYA6HM0003</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -7185,12 +7343,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7222,7 +7380,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTOXSMHM0008</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -7237,12 +7395,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7274,7 +7432,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTOXSNHM0007</t>
+          <t>PTOXSOHM0006</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -7289,12 +7447,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7326,7 +7484,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTOXSOHM0006</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -7341,12 +7499,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7378,7 +7536,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTOXSPHM0005</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -7393,12 +7551,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7430,7 +7588,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTOXS6HM0007</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -7445,12 +7603,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7482,7 +7640,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTOXS7HM0006</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -7497,12 +7655,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7534,7 +7692,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTOXS8HM0005</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -7549,17 +7707,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7579,19 +7737,17 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7601,17 +7757,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES MEDINA</t>
+          <t>SMART INVEST PPR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7631,32 +7787,28 @@
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>PTSXYXHM0003</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7681,7 +7833,7 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="I69" t="n">
         <v>4</v>
@@ -7697,17 +7849,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7727,33 +7879,37 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
-      </c>
-      <c r="J70" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Santander Poupança Prudente FPR</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santander Poupança Prudente</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7773,68 +7929,18 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>1.34</v>
+        <v>1.93</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTYSAVLM0006</t>
+          <t>PTYMCRLM0006</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I72" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -10941,9 +11047,11 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
+        <v>0.83</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4</v>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>PTFP00000762</t>
@@ -10991,9 +11099,11 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>PTFP00000861</t>
@@ -11040,14 +11150,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I61" t="n">
+        <v>4</v>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>PTFP00000416</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>1500</v>
+      </c>
       <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -11086,14 +11202,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3</v>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>PTFP00000424</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>1500</v>
+      </c>
       <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -11132,14 +11254,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>PTFP00000382</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>1500</v>
+      </c>
       <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -11178,14 +11306,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>PTFP00000432</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>1500</v>
+      </c>
       <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -11224,10 +11358,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PTFP00000408</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1500</v>
+      </c>
       <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -11266,14 +11410,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>PTFP00000515</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>1500</v>
+      </c>
       <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -11312,14 +11462,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4</v>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>PTFP00000879</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>1500</v>
+      </c>
       <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -11358,14 +11514,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>PTFP00000507</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>1500</v>
+      </c>
       <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -11404,14 +11566,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>PTFP00000473</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>1500</v>
+      </c>
       <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -11450,10 +11618,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PTFP00000457</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1500</v>
+      </c>
       <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -11809,7 +11987,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11817,7 +11995,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>2.04</v>
       </c>
@@ -14506,14 +14688,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I130" t="n">
+        <v>4</v>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>PTFP00000390</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>1500</v>
+      </c>
       <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -14552,10 +14740,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>5</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>PTFP00000465</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>1500</v>
+      </c>
       <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
@@ -14594,14 +14792,20 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I132" t="n">
+        <v>4</v>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>PTFP00000770</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>1500</v>
+      </c>
       <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
@@ -14643,7 +14847,9 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>1500</v>
+      </c>
       <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
@@ -14682,10 +14888,16 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3</v>
+      </c>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>1500</v>
+      </c>
       <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
@@ -14923,7 +15135,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -14931,22 +15143,14 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
         <v>4</v>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
@@ -14977,7 +15181,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14985,14 +15189,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
         <v>4</v>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,7 +737,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2467,17 +2467,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2501,14 +2501,14 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2521,17 +2521,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2555,14 +2555,14 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2575,17 +2575,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2609,14 +2609,14 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="I41" t="n">
         <v>4</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2629,17 +2629,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2663,14 +2663,14 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.01</v>
+        <v>0.64</v>
       </c>
       <c r="I42" t="n">
         <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -2683,22 +2683,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>casa-inv-sg-founders</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR - Founders</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2713,48 +2713,46 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTCUUBHM0004</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>250000</v>
-      </c>
+          <t>PTCXGPHM0011</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>casa-inv-sg-prime</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR - Prime</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2769,43 +2767,41 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTCUUAHM0005</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTCXGPHM0011</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2825,23 +2821,21 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="I45" t="n">
         <v>4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTYESALM0007</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>25</v>
-      </c>
+          <t>PTCXGPHM0011</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2851,22 +2845,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-plus</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Plus</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2876,49 +2870,51 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTFP00000762</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>PTCXGPHM0011</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-start</t>
+          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Start</t>
+          <t>Caixa Arrojado PPR / OICVM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Caixa Arrojado PPR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2928,49 +2924,51 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTFP00000861</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>PTCXGHHM0011</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-ativa</t>
+          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Ativa</t>
+          <t>Caixa Defensivo PPR / OICVM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Caixa Defensivo PPR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2980,49 +2978,51 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.06</v>
+        <v>1.13</v>
       </c>
       <c r="I48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTFP00000416</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>PTCXGFHM0013</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-conservadora</t>
+          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Conservadora</t>
+          <t>Caixa Moderado PPR / OICVM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Caixa Moderado PPR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3032,49 +3032,51 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTFP00000424</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>PTCXGGHM0012</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-dinamica</t>
+          <t>casa-inv-sg-founders</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Dinâmica</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Founders</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3084,49 +3086,53 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.08</v>
+        <v>1.45</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTFP00000382</t>
+          <t>PTCUUBHM0004</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
+        <v>250000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-equilibrada</t>
+          <t>casa-inv-sg-prime</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Equilibrada</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Prime</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3136,49 +3142,53 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTFP00000432</t>
+          <t>PTCUUAHM0005</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-garantida</t>
+          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Garantida</t>
+          <t>GNB PPR/OICVM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3188,39 +3198,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTFP00000408</t>
+          <t>PTYESALM0007</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-conservadora</t>
+          <t>golden-sgf-etf-plus</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Conservadora</t>
+          <t>Golden SGF ETF Plus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3245,34 +3259,34 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.58</v>
+        <v>0.83</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTFP00000515</t>
+          <t>PTFP00000762</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-dinamica</t>
+          <t>golden-sgf-etf-start</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Dinâmica</t>
+          <t>Golden SGF ETF Start</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3297,18 +3311,18 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="I54" t="n">
         <v>4</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTFP00000879</t>
+          <t>PTFP00000861</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3319,12 +3333,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-equilibrada</t>
+          <t>golden-sgf-poupanca-ativa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Equilibrada</t>
+          <t>Golden SGF Poupança Ativa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3353,14 +3367,14 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTFP00000507</t>
+          <t>PTFP00000416</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3371,12 +3385,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-garantida</t>
+          <t>golden-sgf-poupanca-conservadora</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Garantida</t>
+          <t>Golden SGF Poupança Conservadora</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3405,14 +3419,14 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="I56" t="n">
         <v>3</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PTFP00000473</t>
+          <t>PTFP00000424</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3423,12 +3437,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>golden-sgf-top-gestores</t>
+          <t>golden-sgf-poupanca-dinamica</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Golden SGF TOP GESTORES</t>
+          <t>Golden SGF Poupança Dinâmica</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3457,14 +3471,14 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="I57" t="n">
         <v>4</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTFP00000457</t>
+          <t>PTFP00000382</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3475,22 +3489,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>golden-sgf-poupanca-equilibrada</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>Golden SGF Poupança Equilibrada</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3500,51 +3514,49 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTOPZEHM0017</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000432</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>golden-sgf-poupanca-garantida</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>Golden SGF Poupança Garantida</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3554,51 +3566,49 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.57</v>
+        <v>1.58</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000408</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>golden-sgf-reforma-conservadora</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>Golden SGF Reforma Conservadora</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3608,51 +3618,49 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000515</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>golden-sgf-reforma-dinamica</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>Golden SGF Reforma Dinâmica</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3662,51 +3670,49 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTOPZDHM0000</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000879</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+          <t>golden-sgf-reforma-equilibrada</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+          <t>Golden SGF Reforma Equilibrada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3716,53 +3722,49 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2.19</v>
+        <v>1.58</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTOPZUHM0009</t>
+          <t>PTFP00000507</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+          <t>golden-sgf-reforma-garantida</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+          <t>Golden SGF Reforma Garantida</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3772,53 +3774,49 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTOPZQHM0005</t>
+          <t>PTFP00000473</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>500000</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+          <t>golden-sgf-top-gestores</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+          <t>Golden SGF TOP GESTORES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3828,53 +3826,49 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.47</v>
+        <v>1.58</v>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTOPZVHM0008</t>
+          <t>PTFP00000457</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3884,49 +3878,51 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>PTARMJHM0003</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3936,49 +3932,51 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>2.04</v>
       </c>
       <c r="I66" t="n">
         <v>5</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTFP00000465</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>PTOPZEHM0017</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3988,49 +3986,51 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.58</v>
+        <v>2.57</v>
       </c>
       <c r="I67" t="n">
         <v>4</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTFP00000770</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
+          <t>PTOPZAHM0003</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4040,41 +4040,51 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L68" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PTOPZBHM0002</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sgf-square-acoes</t>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SGF Square Ações</t>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4084,40 +4094,46 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L69" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PTOPZDHM0000</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4137,41 +4153,43 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1.89</v>
+        <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>100000</v>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4191,41 +4209,43 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>10000</v>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4245,41 +4265,43 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>500000</v>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4299,21 +4321,23 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1.39</v>
+        <v>2.47</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1000</v>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4323,52 +4347,570 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>sgf-stoik</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PPR SGF Stoik</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sgf-dr-financas</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SGF DR FINANÇAS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PTFP00000465</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>sgf-deco-proteste</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SGF PPR DECO PROTESTE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>sgf-reforma-stoik</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SGF Reforma Stoik</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>sgf-square-acoes</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SGF Square Ações</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I78" t="n">
+        <v>3</v>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I83" t="n">
+        <v>4</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Santander Aforro PPR/OICVM</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Santander Aforro PPR</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H74" t="n">
+      <c r="H84" t="n">
         <v>0.88</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I84" t="n">
         <v>3</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>PTSFFAHM0013</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
@@ -4385,7 +4927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4687,17 +5229,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
+          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
+          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4716,38 +5258,36 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4767,37 +5307,33 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4817,37 +5353,33 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4867,17 +5399,15 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.64</v>
+        <v>2.09</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>PTIXAFHM0005</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4887,17 +5417,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR / OICVM</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4917,13 +5447,15 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4933,17 +5465,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR / OICVM</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4963,13 +5495,15 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -4979,17 +5513,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR / OICVM</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5009,13 +5543,15 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -5025,17 +5561,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5054,36 +5590,38 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PTGNFHHM0002</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5103,33 +5641,39 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5149,33 +5693,39 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5195,35 +5745,39 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>2.09</v>
+        <v>0.76</v>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5243,35 +5797,39 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>2.08</v>
+        <v>0.76</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5291,35 +5849,39 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PTOYADHM0008</t>
+        </is>
+      </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5339,35 +5901,39 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PTOYAEHM0007</t>
+        </is>
+      </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5387,28 +5953,34 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PTOYAFHM0006</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>100000</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5440,7 +6012,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
+          <t>PTOXCTHM0009</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -5453,12 +6025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5490,7 +6062,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYAIHM0003</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -5505,12 +6077,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5542,7 +6114,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYAJHM0002</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -5557,12 +6129,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5594,7 +6166,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYAKHM0009</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -5609,12 +6181,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5646,7 +6218,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
+          <t>PTOYALHM0008</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -5661,12 +6233,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5698,7 +6270,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOYAMHM0007</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -5713,12 +6285,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5743,19 +6315,17 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5765,12 +6335,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5795,19 +6365,17 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>4</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5817,12 +6385,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5847,14 +6415,14 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>4</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
+          <t>PTOYARHM0002</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -5867,12 +6435,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5897,19 +6465,17 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5919,12 +6485,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5949,19 +6515,17 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYATHM0000</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5971,12 +6535,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6001,19 +6565,17 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>4</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAUHM0007</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6023,12 +6585,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6053,19 +6615,17 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>4</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAVHM0006</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6075,12 +6635,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6105,19 +6665,17 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAWHM0005</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6127,12 +6685,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6157,19 +6715,17 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAXHM0004</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6179,12 +6735,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6216,7 +6772,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTOXS3HM0000</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -6229,12 +6785,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6266,7 +6822,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTOXS4HM0009</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -6279,12 +6835,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6316,7 +6872,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTOYARHM0002</t>
+          <t>PTOXS5HM0008</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -6329,12 +6885,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6358,17 +6914,11 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>PTOYASHM0001</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
@@ -6379,12 +6929,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6409,17 +6959,19 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I41" t="n">
         <v>4</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTOYATHM0000</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2000</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6429,12 +6981,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6459,17 +7011,19 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I42" t="n">
         <v>4</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTOYAUHM0007</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2000</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6479,12 +7033,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6509,17 +7063,19 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I43" t="n">
         <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTOYAVHM0006</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2000</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6529,12 +7085,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6559,17 +7115,19 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOYAWHM0005</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>2000</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6579,12 +7137,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6609,17 +7167,19 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I45" t="n">
         <v>4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOYAXHM0004</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>PTOYA2HM0007</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>2000</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6629,12 +7189,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6659,17 +7219,19 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOXS3HM0000</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>PTOYA3HM0006</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>2000</v>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6679,12 +7241,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6709,17 +7271,19 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I47" t="n">
         <v>4</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTOXS4HM0009</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>PTOYA4HM0005</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>2000</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6729,12 +7293,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6759,17 +7323,19 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I48" t="n">
         <v>4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>PTOYA5HM0004</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>2000</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6779,12 +7345,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6808,12 +7374,20 @@
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I49" t="n">
         <v>4</v>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>PTOYA6HM0003</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>2000</v>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6823,12 +7397,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6860,7 +7434,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTOXTBHM0000</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -6875,12 +7449,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6912,7 +7486,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTOYAYHM0003</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -6927,12 +7501,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6964,7 +7538,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTOYAZHM0002</t>
+          <t>PTOXSOHM0006</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -6979,12 +7553,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7016,7 +7590,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTOYA1HM0008</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -7031,12 +7605,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7068,7 +7642,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTOYA2HM0007</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -7083,12 +7657,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7120,7 +7694,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTOYA3HM0006</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -7135,12 +7709,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7172,7 +7746,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PTOYA4HM0005</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -7187,12 +7761,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7224,7 +7798,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTOYA5HM0004</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -7239,17 +7813,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7269,19 +7843,17 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTOYA6HM0003</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7291,17 +7863,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SMART INVEST PPR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7321,39 +7893,33 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>1.06</v>
+        <v>1.39</v>
       </c>
       <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>PTOXSMHM0008</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>2000</v>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7373,19 +7939,17 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTOXSNHM0007</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7395,17 +7959,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7425,522 +7989,18 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTOXSOHM0006</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>PTOXSPHM0005</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>PTOXS6HM0007</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>PTOXS7HM0006</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>PTOXS8HM0005</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I66" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I67" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>PTSXYXHM0003</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I68" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>SMART INVEST PPR</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I69" t="n">
-        <v>4</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente FPR</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>PTYSAVLM0006</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I71" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -8279,7 +8339,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -10263,7 +10323,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -10271,7 +10331,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>1.13</v>
       </c>
@@ -10280,7 +10344,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -10313,7 +10377,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -10321,7 +10385,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>1.02</v>
       </c>
@@ -10330,7 +10398,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -10363,7 +10431,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -10371,7 +10439,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>0.82</v>
       </c>
@@ -10380,7 +10452,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -10413,7 +10485,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10421,7 +10493,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>0.64</v>
       </c>
@@ -10430,7 +10506,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTIXAFHM0005</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -10484,7 +10560,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -10538,7 +10614,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -10592,7 +10668,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -10646,7 +10722,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTCXGMHM0014</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -10679,7 +10755,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10687,14 +10763,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>2.02</v>
       </c>
       <c r="I52" t="n">
         <v>5</v>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PTCXGHHM0011</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
@@ -10725,7 +10809,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10733,14 +10817,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
         <v>3</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PTCXGFHM0013</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
@@ -10771,7 +10863,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10779,14 +10871,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>1.48</v>
       </c>
       <c r="I54" t="n">
         <v>4</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PTCXGGHM0012</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
@@ -11941,7 +12041,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -11949,14 +12049,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>1.6</v>
       </c>
       <c r="I77" t="n">
         <v>6</v>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PTARMJHM0003</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
@@ -12667,7 +12775,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12675,7 +12783,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>0.76</v>
       </c>
@@ -15135,7 +15247,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15143,14 +15255,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>1.52</v>
       </c>
       <c r="I139" t="n">
         <v>4</v>
       </c>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
@@ -15181,7 +15301,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15189,22 +15309,14 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
         <v>4</v>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
@@ -15235,7 +15347,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15243,14 +15355,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>1.44</v>
       </c>
       <c r="I141" t="n">
         <v>4</v>
       </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4811,12 +4811,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="I83" t="n">
         <v>4</v>
@@ -4865,17 +4865,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Santander Aforro PPR/OICVM</t>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Santander Aforro PPR</t>
+          <t>SMART INVEST PPR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4895,22 +4895,76 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>PTSFFAHM0013</t>
+          <t>PTARMIHM0004</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR/OICVM</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Santander Aforro PPR</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PTSFFAHM0013</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
@@ -4927,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7863,17 +7917,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7893,33 +7947,37 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Santander Poupança Prudente FPR</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santander Poupança Prudente</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7939,68 +7997,18 @@
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1.34</v>
+        <v>1.93</v>
       </c>
       <c r="I60" t="n">
         <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTYSAVLM0006</t>
+          <t>PTYMCRLM0006</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -15301,7 +15309,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15309,14 +15317,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>1.39</v>
       </c>
       <c r="I140" t="n">
         <v>4</v>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,7 +751,9 @@
           <t>PTYINVIM0007</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>50</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -957,7 +959,9 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>PTBZSKHM0003</t>
@@ -975,17 +979,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
+          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
+          <t>BPI Reforma Global Equities PPR/OICVM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BPI Reforma Global</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1005,14 +1009,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTYPIEHM0024</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1025,17 +1033,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
+          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
+          <t>BPI Reforma Investimento PPR/OICVM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BPI Reforma Investimento</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1055,37 +1063,41 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTYPIQLM0008</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
+          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
+          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BPI Reforma Obrigações</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1105,37 +1117,41 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTYPIRLM0007</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
+          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
+          <t>BPI Reforma Valorização PPR/OICVM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bankinter</t>
+          <t>BPI Reforma Valorização</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1155,18 +1171,18 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PTYBCPLM0001</t>
+          <t>PTYPJDLM0002</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1179,12 +1195,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-317</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1212,11 +1228,9 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>1.26</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1226,19 +1240,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-318</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1266,11 +1280,9 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1280,19 +1292,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
+          <t>bankinter-100-ppr-oicvm-fundo-de-investimento-mobiliario-abe-319</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 100 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1320,33 +1332,31 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>2.03</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-320</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1375,14 +1385,14 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1395,12 +1405,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-321</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1429,14 +1439,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTYBCFHM0017</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1449,12 +1459,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
+          <t>bankinter-25-ppr-oicvm-fundo-de-investimento-mobiliario-aber-322</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
+          <t>Bankinter 25 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1483,14 +1493,14 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.39</v>
+        <v>1.1</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCPLM0001</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1503,12 +1513,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-323</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1537,14 +1547,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1557,12 +1567,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-324</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1591,14 +1601,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTYBCQLM0000</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1611,17 +1621,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
+          <t>bankinter-50-ppr-oicvm-fundo-de-investimento-mobiliario-aber-325</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
+          <t>Bankinter 50 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1641,41 +1651,41 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.49</v>
+        <v>1.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTBKCCHM0008</t>
+          <t>PTYBCFHM0017</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-326</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações EUR</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1695,39 +1705,41 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>2.39</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTBKCKHM0008</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-327</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1747,41 +1759,41 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.97</v>
+        <v>1.66</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTYBCDLM0005</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
+          <t>bankinter-75-ppr-oicvm-fundo-de-investimento-mobiliario-aber-328</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
+          <t>Bankinter 75 PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>Bankinter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1801,41 +1813,41 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.64</v>
+        <v>1.56</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTYBCDLM0005</t>
+          <t>PTYBCQLM0000</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
+          <t>bankinter-obrigacoes-eur-2027-ppr-oicvm-fundo-de-investiment-309</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
+          <t>Bankinter Obrigações EUR 2027 PPR / OICVM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bankinter Obrigações PPR</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1859,14 +1871,14 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.68</v>
+        <v>0.49</v>
       </c>
       <c r="I27" t="n">
         <v>3</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTYBCDLM0005</t>
+          <t>PTBKCCHM0008</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1879,17 +1891,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
+          <t>bankinter-obrigacoes-eur-2030-ppr-oicvm-fundo-de-investiment-310</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
+          <t>Bankinter Obrigações EUR 2030 PPR / OICVM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>Bankinter Obrigações EUR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1913,37 +1925,35 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTYBCJHM0013</t>
+          <t>PTBKCKHM0008</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--311</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1967,37 +1977,37 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="I29" t="n">
         <v>3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTYBCJHM0013</t>
+          <t>PTYBCDLM0005</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--312</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bankinter Rendimento PPR</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2021,37 +2031,37 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTYBCJHM0013</t>
+          <t>PTYBCDLM0005</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
+          <t>bankinter-obrigacoes-ppr-oicvm-fundo-de-investimento-aberto--313</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
+          <t>Bankinter Obrigações PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CAIXA AÇÕES LÍDERES</t>
+          <t>Bankinter Obrigações PPR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2071,41 +2081,41 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>0.68</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PTCXGUHM0006</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>100</v>
-      </c>
+          <t>PTYBCDLM0005</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-314</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2125,18 +2135,18 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2.08</v>
+        <v>0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCJHM0013</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2149,17 +2159,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-315</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2179,18 +2189,18 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.9</v>
+        <v>0.54</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCJHM0013</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2203,17 +2213,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
+          <t>bankinter-rendimento-ppr-oicvm-fundo-de-investimento-mobilia-316</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
+          <t>Bankinter Rendimento PPR / OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>Bankinter Rendimento PPR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2233,18 +2243,18 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.52</v>
+        <v>0.47</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
+          <t>PTYBCJHM0013</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2257,17 +2267,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
+          <t>caixa-acoes-lideres-globais-ppr-oicvm-fundo-de-investimento--335</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
+          <t>CAIXA AÇÕES LÍDERES GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH ARROJADO</t>
+          <t>CAIXA AÇÕES LÍDERES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2291,37 +2301,37 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I35" t="n">
-        <v>5</v>
-      </c>
+        <v>1.81</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTCXGBHM0017</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>PTCXGUHM0006</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>100</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-342</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2345,35 +2355,37 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>2.08</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-343</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2397,35 +2409,37 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-344</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH AÇÕES</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2449,35 +2463,37 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTCXGWHM0020</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
+          <t>caixa-wealth-arrojado-ppr-oicvm-fundo-de-investimento-mobili-345</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
+          <t>CAIXA WEALTH ARROJADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>CAIXA WEALTH ARROJADO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2501,14 +2517,14 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTCXGYHM0028</t>
+          <t>PTCXGBHM0017</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2521,17 +2537,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-339</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2555,37 +2571,37 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTCXGYHM0028</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-340</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2609,37 +2625,37 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.82</v>
+        <v>1.68</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTCXGYHM0028</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
+          <t>caixa-wealth-acoes-ppr-oicvm-fundo-de-investimento-mobiliari-341</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
+          <t>CAIXA WEALTH AÇÕES PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH DEFENSIVO</t>
+          <t>CAIXA WEALTH AÇÕES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2663,37 +2679,37 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.64</v>
+        <v>1.47</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTCXGYHM0028</t>
+          <t>PTCXGWHM0020</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-346</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2717,14 +2733,14 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="I43" t="n">
         <v>4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTCXGPHM0011</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -2737,17 +2753,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-347</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2771,14 +2787,14 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTCXGPHM0011</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2791,17 +2807,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-348</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2825,14 +2841,14 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="I45" t="n">
         <v>4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTCXGPHM0011</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -2845,17 +2861,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
+          <t>caixa-wealth-defensivo-ppr-oicvm-fundo-de-investimento-mobil-349</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
+          <t>CAIXA WEALTH DEFENSIVO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CAIXA WEALTH MODERADO</t>
+          <t>CAIXA WEALTH DEFENSIVO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2879,14 +2895,14 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.01</v>
+        <v>0.64</v>
       </c>
       <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTCXGPHM0011</t>
+          <t>PTCXGYHM0028</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -2899,17 +2915,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-350</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR / OICVM</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Caixa Arrojado PPR</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2933,14 +2949,14 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTCXGHHM0011</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -2953,17 +2969,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-351</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR / OICVM</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Caixa Defensivo PPR</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2987,14 +3003,14 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTCXGFHM0013</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3007,17 +3023,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-352</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR / OICVM</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Caixa Moderado PPR</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3041,14 +3057,14 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="I49" t="n">
         <v>4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTCXGGHM0012</t>
+          <t>PTCXGPHM0011</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3061,22 +3077,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>casa-inv-sg-founders</t>
+          <t>caixa-wealth-moderado-ppr-oicvm-fundo-de-investimento-mobili-353</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR - Founders</t>
+          <t>CAIXA WEALTH MODERADO PPR/OICVM - Categoria D</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>CAIXA WEALTH MODERADO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3091,48 +3107,46 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTCUUBHM0004</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>250000</v>
-      </c>
+          <t>PTCXGPHM0011</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>casa-inv-sg-prime</t>
+          <t>caixa-arrojado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-336</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Casa de Investimentos Save &amp; Grow PPR - Prime</t>
+          <t>Caixa Arrojado PPR / OICVM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Casa de Investimentos</t>
+          <t>Caixa Arrojado PPR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>investing</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3147,43 +3161,41 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTCUUAHM0005</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTCXGHHM0011</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
+          <t>caixa-defensivo-ppr-oicvm-fundo-de-investimento-aberto-de-po-337</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM</t>
+          <t>Caixa Defensivo PPR / OICVM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>Caixa Defensivo PPR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3203,23 +3215,21 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTYESALM0007</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>25</v>
-      </c>
+          <t>PTCXGFHM0013</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3229,22 +3239,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-plus</t>
+          <t>caixa-moderado-ppr-oicvm-fundo-de-investimento-aberto-de-pou-338</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Plus</t>
+          <t>Caixa Moderado PPR / OICVM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Caixa Moderado PPR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3254,49 +3264,51 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="I53" t="n">
         <v>4</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>PTFP00000762</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
+          <t>PTCXGGHM0012</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-start</t>
+          <t>casa-inv-sg-founders</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Start</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Founders</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3306,49 +3318,53 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PTFP00000861</t>
+          <t>PTCUUBHM0004</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
+        <v>250000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-ativa</t>
+          <t>casa-inv-sg-prime</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Ativa</t>
+          <t>Casa de Investimentos Save &amp; Grow PPR - Prime</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>Casa de Investimentos</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3358,49 +3374,53 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PTFP00000416</t>
+          <t>PTCUUAHM0005</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-conservadora</t>
+          <t>gnb-ppr-oicvm-fundo-de-investimento-mobiliario-aberto-de-pou-357</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Conservadora</t>
+          <t>GNB PPR/OICVM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3410,39 +3430,43 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="I56" t="n">
         <v>3</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PTFP00000424</t>
+          <t>PTYESALM0007</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-dinamica</t>
+          <t>golden-sgf-etf-plus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Dinâmica</t>
+          <t>Golden SGF ETF Plus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3467,34 +3491,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2.08</v>
+        <v>0.83</v>
       </c>
       <c r="I57" t="n">
         <v>4</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTFP00000382</t>
+          <t>PTFP00000762</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-equilibrada</t>
+          <t>golden-sgf-etf-start</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Equilibrada</t>
+          <t>Golden SGF ETF Start</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3519,18 +3543,18 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="I58" t="n">
         <v>4</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTFP00000432</t>
+          <t>PTFP00000861</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3541,12 +3565,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-garantida</t>
+          <t>golden-sgf-poupanca-ativa</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Garantida</t>
+          <t>Golden SGF Poupança Ativa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3575,14 +3599,14 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PTFP00000408</t>
+          <t>PTFP00000416</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3593,12 +3617,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-conservadora</t>
+          <t>golden-sgf-poupanca-conservadora</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Conservadora</t>
+          <t>Golden SGF Poupança Conservadora</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3634,7 +3658,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTFP00000515</t>
+          <t>PTFP00000424</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3645,12 +3669,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-dinamica</t>
+          <t>golden-sgf-poupanca-dinamica</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Dinâmica</t>
+          <t>Golden SGF Poupança Dinâmica</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3679,14 +3703,14 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTFP00000879</t>
+          <t>PTFP00000382</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3697,12 +3721,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-equilibrada</t>
+          <t>golden-sgf-poupanca-equilibrada</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Equilibrada</t>
+          <t>Golden SGF Poupança Equilibrada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3731,14 +3755,14 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTFP00000507</t>
+          <t>PTFP00000432</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3749,12 +3773,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-garantida</t>
+          <t>golden-sgf-poupanca-garantida</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Garantida</t>
+          <t>Golden SGF Poupança Garantida</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3783,14 +3807,14 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTFP00000473</t>
+          <t>PTFP00000408</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3801,12 +3825,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>golden-sgf-top-gestores</t>
+          <t>golden-sgf-reforma-conservadora</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Golden SGF TOP GESTORES</t>
+          <t>Golden SGF Reforma Conservadora</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3838,11 +3862,11 @@
         <v>1.58</v>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTFP00000457</t>
+          <t>PTFP00000515</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3853,22 +3877,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
+          <t>golden-sgf-reforma-dinamica</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
+          <t>Golden SGF Reforma Dinâmica</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3878,51 +3902,49 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTARMJHM0003</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000879</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>golden-sgf-reforma-equilibrada</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>Golden SGF Reforma Equilibrada</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3932,51 +3954,49 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTOPZEHM0017</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000507</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>golden-sgf-reforma-garantida</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>Golden SGF Reforma Garantida</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3986,51 +4006,49 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.57</v>
+        <v>1.08</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000473</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>golden-sgf-top-gestores</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>Golden SGF TOP GESTORES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4040,46 +4058,44 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="I68" t="n">
         <v>4</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000457</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4103,37 +4119,39 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PTOPZDHM0000</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>PTIGA5HM0003</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>100</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4153,43 +4171,43 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.76</v>
+        <v>1.75</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
+          <t>PTIGA6HM0002</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>100000</v>
+        <v>200</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4213,18 +4231,18 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTOPZUHM0009</t>
+          <t>PTYAIVLM0008</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4235,17 +4253,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4269,18 +4287,18 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTOPZQHM0005</t>
+          <t>PTIG1AHM0006</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>500000</v>
+        <v>200</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4291,17 +4309,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4321,48 +4339,46 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PTOPZVHM0008</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTARMJHM0003</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4372,49 +4388,53 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
+          <t>PTOPZEHM0017</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L74" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4424,49 +4444,53 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>2.57</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PTFP00000465</t>
+          <t>PTOPZAHM0003</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L75" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4476,49 +4500,53 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>PTFP00000770</t>
+          <t>PTOPZBHM0002</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L76" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4528,41 +4556,53 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PTOPZDHM0000</t>
+        </is>
+      </c>
       <c r="K77" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L77" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sgf-square-acoes</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SGF Square Ações</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4572,40 +4612,48 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1.58</v>
+        <v>0.76</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PTOXCUHM0006</t>
+        </is>
+      </c>
       <c r="K78" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
+        <v>100000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4625,41 +4673,43 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>PTOPZUHM0009</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>10000</v>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4679,41 +4729,43 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.39</v>
+        <v>1.11</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>PTOPZQHM0005</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>500000</v>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4733,46 +4785,48 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1.89</v>
+        <v>2.47</v>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>PTOPZVHM0008</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1000</v>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
+          <t>sgf-stoik</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+          <t>PPR SGF Stoik</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4782,51 +4836,49 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="I82" t="n">
         <v>4</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000390</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>sgf-dr-financas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>SGF DR FINANÇAS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4836,51 +4888,49 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000465</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
+          <t>sgf-deco-proteste</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
+          <t>SGF PPR DECO PROTESTE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4890,81 +4940,507 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="I84" t="n">
         <v>4</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>sgf-reforma-stoik</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SGF Reforma Stoik</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>sgf-square-acoes</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SGF Square Ações</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SGF</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>golden_sgf</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FP-PPR</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>250</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SIXTY DEGREES PPR</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PTSXYAHM0000</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I90" t="n">
+        <v>4</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>50</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>50</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>50</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Santander Aforro PPR/OICVM</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Santander Aforro PPR</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H85" t="n">
+      <c r="H93" t="n">
         <v>0.88</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I93" t="n">
         <v>3</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>PTSFFAHM0013</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
@@ -4981,7 +5457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5049,17 +5525,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bpi-reforma-global-equities-ppr-oicvm-fundo-de-investimento--331</t>
+          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPI Reforma Global Equities PPR/OICVM</t>
+          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BPI Reforma Global</t>
+          <t>BlueCrow Global Opportunities</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5079,33 +5555,37 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PTBLWTHM0004</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bpi-reforma-investimento-ppr-oicvm-fundo-de-investimento-abe-332</t>
+          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento PPR/OICVM</t>
+          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BPI Reforma Investimento</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5124,34 +5604,38 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>1.94</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PTGNFHHM0002</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bpi-reforma-obrigacoes-ppr-oicvm-fundo-de-investimento-abert-333</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações PPR/OICVM de Obrigações</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BPI Reforma Obrigações</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5171,33 +5655,35 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.16</v>
+        <v>2.09</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bpi-reforma-valorizacao-ppr-oicvm-fundo-de-investimento-aber-334</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização PPR/OICVM</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BPI Reforma Valorização</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5217,13 +5703,15 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -5233,17 +5721,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bluecrow-global-opportunities-ppr-oia-flexivel-fundo-de-inve-330</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities PPR OIA Flexível</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BlueCrow Global Opportunities</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5263,17 +5751,17 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PTBLWTHM0004</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5283,17 +5771,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5312,36 +5800,40 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PTGNFHHM0002</t>
+          <t>PTOXCSHM0000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>100000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5361,33 +5853,39 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PTOYAAHM0001</t>
+        </is>
+      </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5407,33 +5905,39 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PTOYABHM0000</t>
+        </is>
+      </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5453,35 +5957,39 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>2.09</v>
+        <v>0.76</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PTOYACHM0009</t>
+        </is>
+      </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5501,35 +6009,39 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0.76</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PTOYADHM0008</t>
+        </is>
+      </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5549,35 +6061,39 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PTOYAEHM0007</t>
+        </is>
+      </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5597,30 +6113,34 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.6</v>
+        <v>0.76</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PTOYAFHM0006</t>
+        </is>
+      </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5652,7 +6172,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
+          <t>PTOXCTHM0009</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -5665,12 +6185,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5702,7 +6222,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYAIHM0003</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -5717,12 +6237,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5754,7 +6274,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYAJHM0002</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -5769,12 +6289,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5806,7 +6326,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYAKHM0009</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -5821,12 +6341,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5858,7 +6378,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
+          <t>PTOYALHM0008</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -5873,12 +6393,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5910,7 +6430,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOYAMHM0007</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -5925,12 +6445,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5955,19 +6475,17 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5977,12 +6495,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6007,19 +6525,17 @@
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAQHM0003</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6029,12 +6545,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6059,14 +6575,14 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
+          <t>PTOYARHM0002</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -6079,12 +6595,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6109,19 +6625,17 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYASHM0001</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6131,12 +6645,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6161,19 +6675,17 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYATHM0000</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6183,12 +6695,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6213,19 +6725,17 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>4</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAUHM0007</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6235,12 +6745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6265,19 +6775,17 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>4</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAVHM0006</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6287,12 +6795,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6317,19 +6825,17 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>4</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOYAWHM0005</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6339,12 +6845,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6376,7 +6882,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTOYAXHM0004</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -6389,12 +6895,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6426,7 +6932,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTOXS3HM0000</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -6439,12 +6945,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6476,7 +6982,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTOYARHM0002</t>
+          <t>PTOXS4HM0009</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -6489,12 +6995,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6526,7 +7032,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>PTOYASHM0001</t>
+          <t>PTOXS5HM0008</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -6539,12 +7045,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6568,17 +7074,11 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>4</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>PTOYATHM0000</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
@@ -6589,12 +7089,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6619,17 +7119,19 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I33" t="n">
         <v>4</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTOYAUHM0007</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2000</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6639,12 +7141,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6669,17 +7171,19 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I34" t="n">
         <v>4</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTOYAVHM0006</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>PTOYAYHM0003</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2000</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6689,12 +7193,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6719,17 +7223,19 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I35" t="n">
         <v>4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTOYAWHM0005</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>PTOYAZHM0002</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>2000</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6739,12 +7245,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6769,17 +7275,19 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I36" t="n">
         <v>4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTOYAXHM0004</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>PTOYA1HM0008</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2000</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6789,12 +7297,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6819,17 +7327,19 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I37" t="n">
         <v>4</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTOXS3HM0000</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>PTOYA2HM0007</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>2000</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6839,12 +7349,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6869,17 +7379,19 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I38" t="n">
         <v>4</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTOXS4HM0009</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>PTOYA3HM0006</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2000</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6889,12 +7401,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6919,17 +7431,19 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>PTOYA4HM0005</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>2000</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6939,12 +7453,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6968,12 +7482,20 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PTOYA5HM0004</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>2000</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6983,12 +7505,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7020,7 +7542,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTOXTBHM0000</t>
+          <t>PTOYA6HM0003</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -7035,12 +7557,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7072,7 +7594,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTOYAYHM0003</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -7087,12 +7609,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7124,7 +7646,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTOYAZHM0002</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -7139,12 +7661,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7176,7 +7698,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOYA1HM0008</t>
+          <t>PTOXSOHM0006</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -7191,12 +7713,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7228,7 +7750,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOYA2HM0007</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -7243,12 +7765,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7280,7 +7802,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOYA3HM0006</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -7295,12 +7817,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7332,7 +7854,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTOYA4HM0005</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -7347,12 +7869,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7384,7 +7906,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOYA5HM0004</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -7399,12 +7921,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7436,7 +7958,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTOYA6HM0003</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -7451,17 +7973,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7481,19 +8003,17 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTOXSMHM0008</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7503,17 +8023,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7533,19 +8053,17 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>PTOXSNHM0007</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYSAVLM0006</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7555,17 +8073,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
+          <t>Santander Poupança Valorização FPR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>Santander Poupança Valorização</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7585,430 +8103,18 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PTOXSOHM0006</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I53" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>PTOXSPHM0005</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>PTOXS6HM0007</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>PTOXS7HM0006</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I56" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>PTOXS8HM0005</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>OXY CAPITAL LIQUID</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>SIXTY DEGREES MEDINA</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>PTSXYXHM0003</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente FPR</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>PTYSAVLM0006</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -8361,7 +8467,9 @@
           <t>PTYINVIM0007</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>50</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -8567,7 +8675,9 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>PTBZSKHM0003</t>
@@ -8605,7 +8715,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8613,14 +8723,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>2.21</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PTYPIEHM0024</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
@@ -8651,7 +8769,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8659,14 +8777,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>1.94</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PTYPIQLM0008</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
@@ -8697,7 +8823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8705,14 +8831,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PTYPIRLM0007</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
@@ -8743,7 +8877,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8751,14 +8885,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>2.32</v>
       </c>
       <c r="I14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PTYPJDLM0002</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
@@ -8803,7 +8945,9 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>PTYBCPLM0001</t>
@@ -8853,7 +8997,9 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>PTYBCPLM0001</t>
@@ -8903,7 +9049,9 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>PTYBCPLM0001</t>
@@ -10191,7 +10339,9 @@
       <c r="H41" t="n">
         <v>1.83</v>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>6</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>PTCXGWHM0020</t>
@@ -10243,7 +10393,9 @@
       <c r="H42" t="n">
         <v>1.68</v>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>6</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>PTCXGWHM0020</t>
@@ -10295,7 +10447,9 @@
       <c r="H43" t="n">
         <v>1.47</v>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>PTCXGWHM0020</t>
@@ -11054,7 +11208,7 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -11103,7 +11257,9 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>PTGNFHHM0002</t>
@@ -11765,7 +11921,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -11773,12 +11929,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>1.75</v>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PTIGA5HM0003</t>
+        </is>
+      </c>
       <c r="K71" t="n">
         <v>100</v>
       </c>
@@ -11811,7 +11977,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -11819,14 +11985,24 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>1.75</v>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PTIGA6HM0002</t>
+        </is>
+      </c>
       <c r="K72" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -11953,7 +12129,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -11961,14 +12137,22 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>1.6</v>
       </c>
       <c r="I75" t="n">
         <v>4</v>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PTYAIVLM0008</t>
+        </is>
+      </c>
       <c r="K75" t="n">
         <v>100</v>
       </c>
@@ -12001,7 +12185,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -12009,16 +12193,24 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>1.6</v>
       </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PTIG1AHM0006</t>
+        </is>
+      </c>
       <c r="K76" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -12127,7 +12319,9 @@
           <t>PTOPZEHM0017</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>15</v>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -12181,7 +12375,9 @@
           <t>PTOPZAHM0003</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>15</v>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -12235,7 +12431,9 @@
           <t>PTOPZBHM0002</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>15</v>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -12289,7 +12487,9 @@
           <t>PTOPZDHM0000</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>15</v>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -15110,14 +15310,16 @@
         <v>1.89</v>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>PTSXYAHM0000</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>250</v>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -15164,14 +15366,16 @@
         <v>1.39</v>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>PTSXYAHM0000</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>100000</v>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -15218,14 +15422,16 @@
         <v>1.89</v>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>PTSXYAHM0000</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -15279,7 +15485,9 @@
           <t>PTARMIHM0004</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>50</v>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -15333,7 +15541,9 @@
           <t>PTARMIHM0004</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>50</v>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -15387,7 +15597,9 @@
           <t>PTARMIHM0004</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>50</v>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>

--- a/data/ppr_status.xlsx
+++ b/data/ppr_status.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,7 +807,9 @@
           <t>PTBKCAHM0000</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>500</v>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -861,7 +863,9 @@
           <t>PTBKCAHM0000</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>100000</v>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -915,7 +919,9 @@
           <t>PTBKCAHM0000</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>250000</v>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1237,7 +1243,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>500</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1289,7 +1297,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>100000</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1341,7 +1351,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>250000</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1395,7 +1407,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>500</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1449,7 +1463,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>100000</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1503,7 +1519,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>250000</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1557,7 +1575,9 @@
           <t>PTYBCFHM0017</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>500</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1611,7 +1631,9 @@
           <t>PTYBCFHM0017</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>100000</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1665,7 +1687,9 @@
           <t>PTYBCFHM0017</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>250000</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1719,7 +1743,9 @@
           <t>PTYBCQLM0000</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>500</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1773,7 +1799,9 @@
           <t>PTYBCQLM0000</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>100000</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1827,7 +1855,9 @@
           <t>PTYBCQLM0000</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>250000</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -1987,7 +2017,9 @@
           <t>PTYBCDLM0005</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>500</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2041,7 +2073,9 @@
           <t>PTYBCDLM0005</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>100000</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2095,7 +2129,9 @@
           <t>PTYBCDLM0005</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>250000</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2149,7 +2185,9 @@
           <t>PTYBCJHM0013</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>500</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2203,7 +2241,9 @@
           <t>PTYBCJHM0013</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>100000</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2257,7 +2297,9 @@
           <t>PTYBCJHM0013</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>250000</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2365,7 +2407,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>125000</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2419,7 +2463,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>500000</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2473,7 +2519,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2527,7 +2575,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>5000000</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2581,7 +2631,9 @@
           <t>PTCXGWHM0020</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>125000</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2635,7 +2687,9 @@
           <t>PTCXGWHM0020</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>500000</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2689,7 +2743,9 @@
           <t>PTCXGWHM0020</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2743,7 +2799,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>125000</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2797,7 +2855,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>500000</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2851,7 +2911,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2905,7 +2967,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>5000000</v>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -2959,7 +3023,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>125000</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3013,7 +3079,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>500000</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3067,7 +3135,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3121,7 +3191,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>5000000</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -3461,22 +3533,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-plus</t>
+          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Plus</t>
+          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Golden SGF</t>
+          <t>GNB PPR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3486,39 +3558,41 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>0.83</v>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>PTFP00000762</t>
+          <t>PTGNFHHM0002</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>golden-sgf-etf-start</t>
+          <t>golden-sgf-etf-plus</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Golden SGF ETF Start</t>
+          <t>Golden SGF ETF Plus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3543,34 +3617,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="I58" t="n">
         <v>4</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>PTFP00000861</t>
+          <t>PTFP00000762</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-ativa</t>
+          <t>golden-sgf-etf-start</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Ativa</t>
+          <t>Golden SGF ETF Start</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3595,18 +3669,18 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.06</v>
+        <v>1.08</v>
       </c>
       <c r="I59" t="n">
         <v>4</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>PTFP00000416</t>
+          <t>PTFP00000861</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -3617,12 +3691,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-conservadora</t>
+          <t>golden-sgf-poupanca-ativa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Conservadora</t>
+          <t>Golden SGF Poupança Ativa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3651,14 +3725,14 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PTFP00000424</t>
+          <t>PTFP00000416</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3669,12 +3743,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-dinamica</t>
+          <t>golden-sgf-poupanca-conservadora</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Dinâmica</t>
+          <t>Golden SGF Poupança Conservadora</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3703,14 +3777,14 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PTFP00000382</t>
+          <t>PTFP00000424</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3721,12 +3795,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-equilibrada</t>
+          <t>golden-sgf-poupanca-dinamica</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Equilibrada</t>
+          <t>Golden SGF Poupança Dinâmica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3755,14 +3829,14 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="I62" t="n">
         <v>4</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PTFP00000432</t>
+          <t>PTFP00000382</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3773,12 +3847,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>golden-sgf-poupanca-garantida</t>
+          <t>golden-sgf-poupanca-equilibrada</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Golden SGF Poupança Garantida</t>
+          <t>Golden SGF Poupança Equilibrada</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3807,14 +3881,14 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PTFP00000408</t>
+          <t>PTFP00000432</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3825,12 +3899,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-conservadora</t>
+          <t>golden-sgf-poupanca-garantida</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Conservadora</t>
+          <t>Golden SGF Poupança Garantida</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3866,7 +3940,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PTFP00000515</t>
+          <t>PTFP00000408</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3877,12 +3951,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-dinamica</t>
+          <t>golden-sgf-reforma-conservadora</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Dinâmica</t>
+          <t>Golden SGF Reforma Conservadora</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3914,11 +3988,11 @@
         <v>1.58</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PTFP00000879</t>
+          <t>PTFP00000515</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -3929,12 +4003,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-equilibrada</t>
+          <t>golden-sgf-reforma-dinamica</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Equilibrada</t>
+          <t>Golden SGF Reforma Dinâmica</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3966,11 +4040,11 @@
         <v>1.58</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PTFP00000507</t>
+          <t>PTFP00000879</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -3981,12 +4055,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>golden-sgf-reforma-garantida</t>
+          <t>golden-sgf-reforma-equilibrada</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Golden SGF Reforma Garantida</t>
+          <t>Golden SGF Reforma Equilibrada</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4015,14 +4089,14 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="I67" t="n">
         <v>3</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PTFP00000473</t>
+          <t>PTFP00000507</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4033,12 +4107,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>golden-sgf-top-gestores</t>
+          <t>golden-sgf-reforma-garantida</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Golden SGF TOP GESTORES</t>
+          <t>Golden SGF Reforma Garantida</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4067,14 +4141,14 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>PTFP00000457</t>
+          <t>PTFP00000473</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4085,22 +4159,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
+          <t>golden-sgf-top-gestores</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
+          <t>Golden SGF TOP GESTORES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR</t>
+          <t>Golden SGF</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4110,43 +4184,39 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PTIGA5HM0003</t>
+          <t>PTFP00000457</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>100</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-359</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4182,11 +4252,11 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>PTIGA6HM0002</t>
+          <t>PTIGA5HM0003</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4197,17 +4267,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
+          <t>imga-crescimento-ppr-oicvm-fundo-de-investimento-aberto-de-a-360</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
+          <t>IMGA Crescimento PPR/OICVM - Categoria FR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR</t>
+          <t>IMGA Crescimento PPR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4231,34 +4301,34 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PTYAIVLM0008</t>
+          <t>PTIGA6HM0002</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-363</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4294,11 +4364,11 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PTIG1AHM0006</t>
+          <t>PTYAIVLM0008</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4309,17 +4379,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
+          <t>imga-poupanca-ppr-oicvm-fundo-de-investimento-aberto-de-poup-364</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
+          <t>IMGA Poupança PPR / OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INVEST TENDÊNCIAS GLOBAIS</t>
+          <t>IMGA Poupança PPR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4339,41 +4409,43 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H73" t="n">
         <v>1.6</v>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PTARMJHM0003</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>PTIG1AHM0006</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>200</v>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
+          <t>invest-tendencias-globais-ppr-oicvm-fundo-de-investimento-mo-365</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS PPR/OICVM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR</t>
+          <t>INVEST TENDÊNCIAS GLOBAIS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4393,38 +4465,36 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>PTOPZEHM0017</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>15</v>
-      </c>
+          <t>PTARMJHM0003</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
+          <t>optimize-ppr-oicvm-agressivo-fundo-de-investimento-aberto-de-369</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM ATIVO</t>
+          <t>OPTIMIZE PPR/OICVM AGRESSIVO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4453,14 +4523,14 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>PTOPZAHM0003</t>
+          <t>PTOPZEHM0017</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4475,12 +4545,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
+          <t>optimize-ppr-oicvm-ativo-fundo-de-investimento-aberto-de-pou-370</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
+          <t>OPTIMIZE PPR/OICVM ATIVO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4490,7 +4560,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4509,14 +4579,14 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>PTOPZBHM0002</t>
+          <t>PTOPZAHM0003</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4531,12 +4601,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
+          <t>optimize-ppr-oicvm-equilibrado-fundo-de-investimento-aberto--371</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OPTIMIZE PPR/OICVM MODERADO</t>
+          <t>OPTIMIZE PPR/OICVM EQUILIBRADO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4565,14 +4635,14 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1.81</v>
+        <v>2.36</v>
       </c>
       <c r="I77" t="n">
         <v>4</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>PTOPZDHM0000</t>
+          <t>PTOPZBHM0002</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -4587,17 +4657,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
+          <t>optimize-ppr-oicvm-moderado-fundo-de-investimento-aberto-de--372</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
+          <t>OPTIMIZE PPR/OICVM MODERADO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>OPTIMIZE PPR</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4617,43 +4687,43 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.76</v>
+        <v>1.81</v>
       </c>
       <c r="I78" t="n">
         <v>4</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>PTOXCUHM0006</t>
+          <t>PTOPZDHM0000</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>100000</v>
+        <v>15</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-382</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4673,38 +4743,38 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.19</v>
+        <v>0.76</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PTOPZUHM0009</t>
+          <t>PTOXCUHM0006</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-366</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria D</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4733,18 +4803,18 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.11</v>
+        <v>2.19</v>
       </c>
       <c r="I80" t="n">
         <v>5</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>PTOPZQHM0005</t>
+          <t>PTOPZUHM0009</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>500000</v>
+        <v>10000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4755,12 +4825,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-367</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria P</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4789,18 +4859,18 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.47</v>
+        <v>1.11</v>
       </c>
       <c r="I81" t="n">
         <v>5</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>PTOPZVHM0008</t>
+          <t>PTOPZQHM0005</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>1000</v>
+        <v>500000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4811,22 +4881,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sgf-stoik</t>
+          <t>optimize-lfo-ppr-oicvm-leopardo-fundo-de-investimento-aberto-368</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PPR SGF Stoik</t>
+          <t>Optimize LFO PPR/OICVM Leopardo - Categoria S</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SGF</t>
+          <t>Optimize LFO PPR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>golden_sgf</t>
+          <t>cmvm</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4836,39 +4906,43 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FP-PPR</t>
+          <t>FI-PPR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1.08</v>
+        <v>2.47</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>PTFP00000390</t>
+          <t>PTOPZVHM0008</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L82" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>sgf-dr-financas</t>
+          <t>sgf-stoik</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SGF DR FINANÇAS</t>
+          <t>PPR SGF Stoik</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4897,14 +4971,14 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>PTFP00000465</t>
+          <t>PTFP00000390</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4915,12 +4989,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sgf-deco-proteste</t>
+          <t>sgf-dr-financas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SGF PPR DECO PROTESTE</t>
+          <t>SGF DR FINANÇAS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4949,14 +5023,14 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>PTFP00000770</t>
+          <t>PTFP00000465</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -4967,12 +5041,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sgf-reforma-stoik</t>
+          <t>sgf-deco-proteste</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SGF Reforma Stoik</t>
+          <t>SGF PPR DECO PROTESTE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5000,9 +5074,17 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I85" t="n">
+        <v>4</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PTFP00000770</t>
+        </is>
+      </c>
       <c r="K85" t="n">
         <v>1500</v>
       </c>
@@ -5011,12 +5093,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>sgf-square-acoes</t>
+          <t>sgf-reforma-stoik</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SGF Square Ações</t>
+          <t>SGF Reforma Stoik</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5044,12 +5126,8 @@
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="H86" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I86" t="n">
-        <v>3</v>
-      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
         <v>1500</v>
@@ -5059,22 +5137,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
+          <t>sgf-square-acoes</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
+          <t>SGF Square Ações</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR</t>
+          <t>SGF</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>golden_sgf</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5084,43 +5162,35 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI-PPR</t>
+          <t>FP-PPR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>PTSXYAHM0000</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
-        <v>250</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
-        </is>
-      </c>
+        <v>1500</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-415</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria C</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5149,7 +5219,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="I88" t="n">
         <v>2</v>
@@ -5160,7 +5230,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>100000</v>
+        <v>250</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5171,12 +5241,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-416</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5205,7 +5275,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="I89" t="n">
         <v>2</v>
@@ -5216,7 +5286,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5227,17 +5297,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-conservador-418</t>
+          <t>sixty-degrees-ppr-oicvm-flexivel-fundo-de-investimento-mobil-417</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
+          <t>SIXTY DEGREES PPR/OICVM Flexível - Categoria R</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR</t>
+          <t>SIXTY DEGREES PPR</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5261,34 +5331,34 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>PTARMIHM0004</t>
+          <t>PTSXYAHM0000</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS FLEXÍVEIS DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-dinamico-419</t>
+          <t>smart-invest-ppr-oicvm-conservador-418</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
+          <t>SMART INVEST PPR/OICVM CONSERVADOR</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5317,7 +5387,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="I91" t="n">
         <v>4</v>
@@ -5339,12 +5409,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>smart-invest-ppr-oicvm-moderado-420</t>
+          <t>smart-invest-ppr-oicvm-dinamico-419</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SMART INVEST PPR/OICVM MODERADO</t>
+          <t>SMART INVEST PPR/OICVM DINÂMICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5373,7 +5443,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="I92" t="n">
         <v>4</v>
@@ -5395,54 +5465,164 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>smart-invest-ppr-oicvm-moderado-420</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR/OICVM MODERADO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SMART INVEST PPR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I93" t="n">
+        <v>4</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PTARMIHM0004</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>50</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>fundo-de-investimento-mobiliario-aberto-de-obrigacoes-de-pou-356</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Santander Aforro PPR/OICVM</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Santander Aforro PPR</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>cmvm</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H93" t="n">
+      <c r="H94" t="n">
         <v>0.88</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I94" t="n">
         <v>3</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>PTSFFAHM0013</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Santander Poupança Valorização FPR</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Santander Poupança Valorização</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>investing</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FI-PPR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>PTYMCRLM0006</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5575,17 +5755,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gnb-ppr-oicvm-global-equities-opportunities-fundo-de-investi-358</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GNB PPR/OICVM Global Equities Opportunities de Ações</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GNB PPR</t>
+          <t>IMGA Investimento PPR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5604,33 +5784,31 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2.09</v>
+      </c>
       <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>PTGNFHHM0002</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--361</t>
+          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria A</t>
+          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5655,7 +5833,7 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -5673,17 +5851,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>imga-investimento-ppr-oicvm-fundo-de-investimento-aberto-de--362</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR/OICVM - Categoria R</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IMGA Investimento PPR</t>
+          <t>OXY CAPITAL LIQUID</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5703,30 +5881,32 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2.08</v>
+        <v>0.16</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>100</v>
-      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PTOXCRHM0001</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
+          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-373</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria AA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5751,17 +5931,19 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PTOXCRHM0001</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>PTOXCSHM0000</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>100000</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -5771,12 +5953,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-374</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5808,7 +5990,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PTOXCSHM0000</t>
+          <t>PTOYAAHM0001</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -5823,12 +6005,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-375</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5860,7 +6042,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PTOYAAHM0001</t>
+          <t>PTOYABHM0000</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -5875,12 +6057,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-376</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5912,7 +6094,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PTOYABHM0000</t>
+          <t>PTOYACHM0009</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -5927,12 +6109,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-377</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5964,7 +6146,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PTOYACHM0009</t>
+          <t>PTOYADHM0008</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -5979,12 +6161,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-378</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6016,7 +6198,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PTOYADHM0008</t>
+          <t>PTOYAEHM0007</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -6031,12 +6213,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-379</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6068,7 +6250,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PTOYAEHM0007</t>
+          <t>PTOYAFHM0006</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -6083,12 +6265,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-380</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria BG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6113,19 +6295,17 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.76</v>
+        <v>0.16</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PTOYAFHM0006</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXCTHM0009</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6135,12 +6315,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-381</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria CA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6165,17 +6345,19 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PTOXCTHM0009</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>PTOYAIHM0003</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>100000</v>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6185,12 +6367,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-383</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6222,7 +6404,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PTOYAIHM0003</t>
+          <t>PTOYAJHM0002</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -6237,12 +6419,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-384</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6274,7 +6456,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PTOYAJHM0002</t>
+          <t>PTOYAKHM0009</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -6289,12 +6471,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-385</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6326,7 +6508,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PTOYAKHM0009</t>
+          <t>PTOYALHM0008</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -6341,12 +6523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-501</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6378,7 +6560,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PTOYALHM0008</t>
+          <t>PTOYAMHM0007</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -6393,12 +6575,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-502</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria DF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6423,19 +6605,17 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PTOYAMHM0007</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100000</v>
-      </c>
+          <t>PTOXTAHM0001</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -6445,12 +6625,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-386</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6482,7 +6662,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTOXTAHM0001</t>
+          <t>PTOYAQHM0003</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -6495,12 +6675,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-387</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6532,7 +6712,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PTOYAQHM0003</t>
+          <t>PTOYARHM0002</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -6545,12 +6725,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-388</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6582,7 +6762,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTOYARHM0002</t>
+          <t>PTOYASHM0001</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -6595,12 +6775,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-389</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria ED</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6632,7 +6812,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PTOYASHM0001</t>
+          <t>PTOYATHM0000</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -6645,12 +6825,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-390</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6682,7 +6862,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PTOYATHM0000</t>
+          <t>PTOYAUHM0007</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -6695,12 +6875,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-391</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6732,7 +6912,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PTOYAUHM0007</t>
+          <t>PTOYAVHM0006</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -6745,12 +6925,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-392</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6782,7 +6962,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PTOYAVHM0006</t>
+          <t>PTOYAWHM0005</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -6795,12 +6975,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-393</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6832,7 +7012,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PTOYAWHM0005</t>
+          <t>PTOYAXHM0004</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -6845,12 +7025,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-394</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6882,7 +7062,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PTOYAXHM0004</t>
+          <t>PTOXS3HM0000</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -6895,12 +7075,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-395</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6932,7 +7112,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PTOXS3HM0000</t>
+          <t>PTOXS4HM0009</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -6945,12 +7125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-396</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6982,7 +7162,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PTOXS4HM0009</t>
+          <t>PTOXS5HM0008</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -6995,12 +7175,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-503</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7024,17 +7204,11 @@
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>4</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>PTOXS5HM0008</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
@@ -7045,12 +7219,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-504</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria EM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7074,12 +7248,20 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>1.06</v>
+      </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PTOXTBHM0000</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>2000</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7089,12 +7271,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-397</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FA</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7126,7 +7308,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>PTOXTBHM0000</t>
+          <t>PTOYAYHM0003</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -7141,12 +7323,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-398</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FB</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7178,7 +7360,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PTOYAYHM0003</t>
+          <t>PTOYAZHM0002</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -7193,12 +7375,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-399</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FC</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7230,7 +7412,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PTOYAZHM0002</t>
+          <t>PTOYA1HM0008</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -7245,12 +7427,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-400</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FD</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7282,7 +7464,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PTOYA1HM0008</t>
+          <t>PTOYA2HM0007</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -7297,12 +7479,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-401</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FE</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7334,7 +7516,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PTOYA2HM0007</t>
+          <t>PTOYA3HM0006</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -7349,12 +7531,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-402</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FF</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7386,7 +7568,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>PTOYA3HM0006</t>
+          <t>PTOYA4HM0005</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -7401,12 +7583,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-403</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FG</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7438,7 +7620,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>PTOYA4HM0005</t>
+          <t>PTOYA5HM0004</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -7453,12 +7635,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-404</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FH</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7490,7 +7672,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PTOYA5HM0004</t>
+          <t>PTOYA6HM0003</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7505,12 +7687,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-405</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FI</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7542,7 +7724,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PTOYA6HM0003</t>
+          <t>PTOXSMHM0008</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -7557,12 +7739,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-406</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FJ</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7594,7 +7776,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>PTOXSMHM0008</t>
+          <t>PTOXSNHM0007</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -7609,12 +7791,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-407</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FK</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7646,7 +7828,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>PTOXSNHM0007</t>
+          <t>PTOXSOHM0006</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -7661,12 +7843,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-408</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FL</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7698,7 +7880,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PTOXSOHM0006</t>
+          <t>PTOXSPHM0005</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -7713,12 +7895,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-409</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FM</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7750,7 +7932,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PTOXSPHM0005</t>
+          <t>PTOXS6HM0007</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -7765,12 +7947,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-410</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FN</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7802,7 +7984,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PTOXS6HM0007</t>
+          <t>PTOXS7HM0006</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -7817,12 +7999,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-411</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FO</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7854,7 +8036,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PTOXS7HM0006</t>
+          <t>PTOXS8HM0005</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -7869,12 +8051,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-505</t>
+          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FP</t>
+          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7906,7 +8088,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>PTOXS8HM0005</t>
+          <t>PTOXS9HM0004</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -7921,17 +8103,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>oxy-capital-liquid-opportunities-a-ppr-fundo-de-investimento-506</t>
+          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID OPPORTUNITIES A, PPR - Categoria FQ</t>
+          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OXY CAPITAL LIQUID</t>
+          <t>SIXTY DEGREES MEDINA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7951,19 +8133,17 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PTOXS9HM0004</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>2000</v>
-      </c>
+          <t>PTSXYXHM0003</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
@@ -7973,17 +8153,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sixty-degrees-medina-ppr-oiavm-flexivel-fundo-de-investiment-414</t>
+          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES MEDINA PPR OIAVM FLEXÍVEL Flexível - Categoria I</t>
+          <t>Santander Poupança Prudente FPR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SIXTY DEGREES MEDINA</t>
+          <t>Santander Poupança Prudente</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8003,118 +8183,18 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="I50" t="n">
         <v>3</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>PTSXYXHM0003</t>
+          <t>PTYSAVLM0006</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-354</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente FPR</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Santander Poupança Prudente</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>PTYSAVLM0006</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fundo-de-investimento-alternativo-aberto-de-poupanca-reforma-355</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização FPR</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Santander Poupança Valorização</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>cmvm</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>FI-PPR</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>PTYMCRLM0006</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA NÃO HARMONIZADOS</t>
         </is>
@@ -8523,7 +8603,9 @@
           <t>PTBKCAHM0000</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>500</v>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -8577,7 +8659,9 @@
           <t>PTBKCAHM0000</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>100000</v>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -8631,7 +8715,9 @@
           <t>PTBKCAHM0000</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>250000</v>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -8953,7 +9039,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>500</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9005,7 +9093,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>100000</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9057,7 +9147,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>250000</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9111,7 +9203,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>500</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9165,7 +9259,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>100000</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9219,7 +9315,9 @@
           <t>PTYBCPLM0001</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>250000</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9273,7 +9371,9 @@
           <t>PTYBCFHM0017</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>500</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9327,7 +9427,9 @@
           <t>PTYBCFHM0017</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>100000</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9381,7 +9483,9 @@
           <t>PTYBCFHM0017</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>250000</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9435,7 +9539,9 @@
           <t>PTYBCQLM0000</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>500</v>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9489,7 +9595,9 @@
           <t>PTYBCQLM0000</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>100000</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9543,7 +9651,9 @@
           <t>PTYBCQLM0000</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>250000</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9703,7 +9813,9 @@
           <t>PTYBCDLM0005</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>500</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9757,7 +9869,9 @@
           <t>PTYBCDLM0005</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>100000</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9811,7 +9925,9 @@
           <t>PTYBCDLM0005</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>250000</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>FUNDOS DE OBRIGAÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9865,7 +9981,9 @@
           <t>PTYBCJHM0013</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>500</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9919,7 +10037,9 @@
           <t>PTYBCJHM0013</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>100000</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -9973,7 +10093,9 @@
           <t>PTYBCJHM0013</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>250000</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10131,7 +10253,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>125000</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10185,7 +10309,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>500000</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10239,7 +10365,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10293,7 +10421,9 @@
           <t>PTCXGBHM0017</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>5000000</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10347,7 +10477,9 @@
           <t>PTCXGWHM0020</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>125000</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10401,7 +10533,9 @@
           <t>PTCXGWHM0020</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>500000</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10455,7 +10589,9 @@
           <t>PTCXGWHM0020</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>FUNDOS DE AÇÕES DE FUNDOS POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10509,7 +10645,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>125000</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10563,7 +10701,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>500000</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10617,7 +10757,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10671,7 +10813,9 @@
           <t>PTCXGYHM0028</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="n">
+        <v>5000000</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10725,7 +10869,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>125000</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10779,7 +10925,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>500000</v>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10833,7 +10981,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>1000000</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -10887,7 +11037,9 @@
           <t>PTCXGPHM0011</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>5000000</v>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>FUNDOS DE POUPANÇA-REFORMA HARMONIZADOS</t>
@@ -11242,12 +11394,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11255,7 +11407,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>3</v>
@@ -12346,7 +12502,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -15728,12 +15884,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>investing</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>cmvm</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -15741,7 +15897,11 @@
           <t>FI-PPR</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>1.93</v>
       </c>
